--- a/review-results/复盘信息抓取-20260904.xlsx
+++ b/review-results/复盘信息抓取-20260904.xlsx
@@ -1125,13 +1125,29 @@
           <t>0015</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n"/>
+      <c r="D2" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E2" s="3" t="n">
         <v>414.11</v>
       </c>
       <c r="I2" s="3" t="n"/>
-      <c r="M2" s="3" t="n"/>
-      <c r="O2" s="3" t="n"/>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0015</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>372.69</v>
+      </c>
       <c r="S2" s="3" t="n"/>
       <c r="T2" s="3" t="n"/>
     </row>
@@ -1149,13 +1165,29 @@
           <t>0030</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n"/>
+      <c r="D3" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E3" s="3" t="n">
         <v>412.97</v>
       </c>
       <c r="I3" s="3" t="n"/>
-      <c r="M3" s="3" t="n"/>
-      <c r="O3" s="3" t="n"/>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0030</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>372.69</v>
+      </c>
       <c r="S3" s="3" t="n"/>
       <c r="T3" s="3" t="n"/>
     </row>
@@ -1173,13 +1205,29 @@
           <t>0045</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n"/>
+      <c r="D4" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E4" s="3" t="n">
         <v>409.23</v>
       </c>
       <c r="I4" s="3" t="n"/>
-      <c r="M4" s="3" t="n"/>
-      <c r="O4" s="3" t="n"/>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>372.69</v>
+      </c>
       <c r="S4" s="3" t="n"/>
       <c r="T4" s="3" t="n"/>
     </row>
@@ -1197,14 +1245,30 @@
           <t>0100</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n"/>
+      <c r="D5" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E5" s="3" t="n">
         <v>413.29</v>
       </c>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="n"/>
-      <c r="M5" s="3" t="n"/>
-      <c r="O5" s="3" t="n"/>
+      <c r="L5" t="n">
+        <v>4</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0100</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>372.69</v>
+      </c>
       <c r="S5" s="3" t="n"/>
       <c r="T5" s="3" t="n"/>
     </row>
@@ -1222,14 +1286,30 @@
           <t>0115</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n"/>
+      <c r="D6" s="3" t="n">
+        <v>345.5</v>
+      </c>
       <c r="E6" s="3" t="n">
         <v>415.08</v>
       </c>
       <c r="H6" s="3" t="n"/>
       <c r="I6" s="3" t="n"/>
-      <c r="M6" s="3" t="n"/>
-      <c r="O6" s="3" t="n"/>
+      <c r="L6" t="n">
+        <v>5</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0115</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>377.35</v>
+      </c>
       <c r="S6" s="3" t="n"/>
       <c r="T6" s="3" t="n"/>
     </row>
@@ -1247,14 +1327,30 @@
           <t>0130</t>
         </is>
       </c>
-      <c r="D7" s="3" t="n"/>
+      <c r="D7" s="3" t="n">
+        <v>345.5</v>
+      </c>
       <c r="E7" s="3" t="n">
         <v>412.01</v>
       </c>
       <c r="H7" s="3" t="n"/>
       <c r="I7" s="3" t="n"/>
-      <c r="M7" s="3" t="n"/>
-      <c r="O7" s="3" t="n"/>
+      <c r="L7" t="n">
+        <v>6</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0130</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>377.35</v>
+      </c>
       <c r="S7" s="3" t="n"/>
       <c r="T7" s="3" t="n"/>
     </row>
@@ -1272,14 +1368,30 @@
           <t>0145</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n"/>
+      <c r="D8" s="3" t="n">
+        <v>345.5</v>
+      </c>
       <c r="E8" s="3" t="n">
         <v>405.2</v>
       </c>
       <c r="H8" s="3" t="n"/>
       <c r="I8" s="3" t="n"/>
-      <c r="M8" s="3" t="n"/>
-      <c r="O8" s="3" t="n"/>
+      <c r="L8" t="n">
+        <v>7</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0145</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>377.35</v>
+      </c>
       <c r="S8" s="3" t="n"/>
       <c r="T8" s="3" t="n"/>
     </row>
@@ -1297,14 +1409,30 @@
           <t>0200</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n"/>
+      <c r="D9" s="3" t="n">
+        <v>351.14</v>
+      </c>
       <c r="E9" s="3" t="n">
         <v>397.36</v>
       </c>
       <c r="H9" s="3" t="n"/>
       <c r="I9" s="3" t="n"/>
-      <c r="M9" s="3" t="n"/>
-      <c r="O9" s="3" t="n"/>
+      <c r="L9" t="n">
+        <v>8</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0200</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>377.35</v>
+      </c>
       <c r="S9" s="3" t="n"/>
       <c r="T9" s="3" t="n"/>
     </row>
@@ -1322,14 +1450,30 @@
           <t>0215</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n"/>
+      <c r="D10" s="3" t="n">
+        <v>351.14</v>
+      </c>
       <c r="E10" s="3" t="n">
         <v>401.69</v>
       </c>
       <c r="H10" s="3" t="n"/>
       <c r="I10" s="3" t="n"/>
-      <c r="M10" s="3" t="n"/>
-      <c r="O10" s="3" t="n"/>
+      <c r="L10" t="n">
+        <v>9</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>377.35</v>
+      </c>
       <c r="S10" s="3" t="n"/>
       <c r="T10" s="3" t="n"/>
     </row>
@@ -1347,14 +1491,30 @@
           <t>0230</t>
         </is>
       </c>
-      <c r="D11" s="3" t="n"/>
+      <c r="D11" s="3" t="n">
+        <v>351.14</v>
+      </c>
       <c r="E11" s="3" t="n">
         <v>411.85</v>
       </c>
       <c r="H11" s="3" t="n"/>
       <c r="I11" s="3" t="n"/>
-      <c r="M11" s="3" t="n"/>
-      <c r="O11" s="3" t="n"/>
+      <c r="L11" t="n">
+        <v>10</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0230</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>377.35</v>
+      </c>
       <c r="S11" s="3" t="n"/>
       <c r="T11" s="3" t="n"/>
     </row>
@@ -1372,14 +1532,30 @@
           <t>0245</t>
         </is>
       </c>
-      <c r="D12" s="3" t="n"/>
+      <c r="D12" s="3" t="n">
+        <v>351.14</v>
+      </c>
       <c r="E12" s="3" t="n">
         <v>403.22</v>
       </c>
       <c r="H12" s="3" t="n"/>
       <c r="I12" s="3" t="n"/>
-      <c r="M12" s="3" t="n"/>
-      <c r="O12" s="3" t="n"/>
+      <c r="L12" t="n">
+        <v>11</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>377.35</v>
+      </c>
       <c r="S12" s="3" t="n"/>
       <c r="T12" s="3" t="n"/>
     </row>
@@ -1397,14 +1573,30 @@
           <t>0300</t>
         </is>
       </c>
-      <c r="D13" s="3" t="n"/>
+      <c r="D13" s="3" t="n">
+        <v>345.5</v>
+      </c>
       <c r="E13" s="3" t="n">
         <v>396.26</v>
       </c>
       <c r="H13" s="3" t="n"/>
       <c r="I13" s="3" t="n"/>
-      <c r="M13" s="3" t="n"/>
-      <c r="O13" s="3" t="n"/>
+      <c r="L13" t="n">
+        <v>12</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0300</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>377.35</v>
+      </c>
       <c r="S13" s="3" t="n"/>
       <c r="T13" s="3" t="n"/>
     </row>
@@ -1422,13 +1614,29 @@
           <t>0315</t>
         </is>
       </c>
-      <c r="D14" s="3" t="n"/>
+      <c r="D14" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E14" s="3" t="n">
         <v>403.35</v>
       </c>
       <c r="I14" s="3" t="n"/>
-      <c r="M14" s="3" t="n"/>
-      <c r="O14" s="3" t="n"/>
+      <c r="L14" t="n">
+        <v>13</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0315</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>377.35</v>
+      </c>
       <c r="S14" s="3" t="n"/>
       <c r="T14" s="3" t="n"/>
     </row>
@@ -1446,13 +1654,29 @@
           <t>0330</t>
         </is>
       </c>
-      <c r="D15" s="3" t="n"/>
+      <c r="D15" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E15" s="3" t="n">
         <v>396.26</v>
       </c>
       <c r="I15" s="3" t="n"/>
-      <c r="M15" s="3" t="n"/>
-      <c r="O15" s="3" t="n"/>
+      <c r="L15" t="n">
+        <v>14</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0330</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>377.35</v>
+      </c>
       <c r="S15" s="3" t="n"/>
       <c r="T15" s="3" t="n"/>
     </row>
@@ -1470,13 +1694,29 @@
           <t>0345</t>
         </is>
       </c>
-      <c r="D16" s="3" t="n"/>
+      <c r="D16" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E16" s="3" t="n">
         <v>397.64</v>
       </c>
       <c r="I16" s="3" t="n"/>
-      <c r="M16" s="3" t="n"/>
-      <c r="O16" s="3" t="n"/>
+      <c r="L16" t="n">
+        <v>15</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0345</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>377.35</v>
+      </c>
       <c r="S16" s="3" t="n"/>
       <c r="T16" s="3" t="n"/>
     </row>
@@ -1494,13 +1734,29 @@
           <t>0400</t>
         </is>
       </c>
-      <c r="D17" s="3" t="n"/>
+      <c r="D17" s="3" t="n">
+        <v>345.5</v>
+      </c>
       <c r="E17" s="3" t="n">
         <v>403.89</v>
       </c>
       <c r="I17" s="3" t="n"/>
-      <c r="M17" s="3" t="n"/>
-      <c r="O17" s="3" t="n"/>
+      <c r="L17" t="n">
+        <v>16</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0400</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>372.69</v>
+      </c>
       <c r="S17" s="3" t="n"/>
       <c r="T17" s="3" t="n"/>
     </row>
@@ -1518,13 +1774,29 @@
           <t>0415</t>
         </is>
       </c>
-      <c r="D18" s="3" t="n"/>
+      <c r="D18" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E18" s="3" t="n">
         <v>403.22</v>
       </c>
       <c r="I18" s="3" t="n"/>
-      <c r="M18" s="3" t="n"/>
-      <c r="O18" s="3" t="n"/>
+      <c r="L18" t="n">
+        <v>17</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0415</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>372.69</v>
+      </c>
       <c r="S18" s="3" t="n"/>
       <c r="T18" s="3" t="n"/>
     </row>
@@ -1542,14 +1814,30 @@
           <t>0430</t>
         </is>
       </c>
-      <c r="D19" s="3" t="n"/>
+      <c r="D19" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E19" s="3" t="n">
         <v>403.35</v>
       </c>
       <c r="H19" s="3" t="n"/>
       <c r="I19" s="3" t="n"/>
-      <c r="M19" s="3" t="n"/>
-      <c r="O19" s="3" t="n"/>
+      <c r="L19" t="n">
+        <v>18</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0430</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>372.69</v>
+      </c>
       <c r="S19" s="3" t="n"/>
       <c r="T19" s="3" t="n"/>
     </row>
@@ -1567,14 +1855,30 @@
           <t>0445</t>
         </is>
       </c>
-      <c r="D20" s="3" t="n"/>
+      <c r="D20" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E20" s="3" t="n">
         <v>403.35</v>
       </c>
       <c r="H20" s="3" t="n"/>
       <c r="I20" s="3" t="n"/>
-      <c r="M20" s="3" t="n"/>
-      <c r="O20" s="3" t="n"/>
+      <c r="L20" t="n">
+        <v>19</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0445</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>372.69</v>
+      </c>
       <c r="S20" s="3" t="n"/>
       <c r="T20" s="3" t="n"/>
     </row>
@@ -1592,14 +1896,30 @@
           <t>0500</t>
         </is>
       </c>
-      <c r="D21" s="3" t="n"/>
+      <c r="D21" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E21" s="3" t="n">
         <v>403.47</v>
       </c>
       <c r="H21" s="3" t="n"/>
       <c r="I21" s="3" t="n"/>
-      <c r="M21" s="3" t="n"/>
-      <c r="O21" s="3" t="n"/>
+      <c r="L21" t="n">
+        <v>20</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0500</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>372.69</v>
+      </c>
       <c r="S21" s="3" t="n"/>
       <c r="T21" s="3" t="n"/>
     </row>
@@ -1617,14 +1937,30 @@
           <t>0515</t>
         </is>
       </c>
-      <c r="D22" s="3" t="n"/>
+      <c r="D22" s="3" t="n">
+        <v>369.79</v>
+      </c>
       <c r="E22" s="3" t="n">
         <v>403.47</v>
       </c>
       <c r="H22" s="3" t="n"/>
       <c r="I22" s="3" t="n"/>
-      <c r="M22" s="3" t="n"/>
-      <c r="O22" s="3" t="n"/>
+      <c r="L22" t="n">
+        <v>21</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0515</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>407.63</v>
+      </c>
       <c r="S22" s="3" t="n"/>
       <c r="T22" s="3" t="n"/>
     </row>
@@ -1642,14 +1978,30 @@
           <t>0530</t>
         </is>
       </c>
-      <c r="D23" s="3" t="n"/>
+      <c r="D23" s="3" t="n">
+        <v>369.79</v>
+      </c>
       <c r="E23" s="3" t="n">
         <v>410.83</v>
       </c>
       <c r="H23" s="3" t="n"/>
       <c r="I23" s="3" t="n"/>
-      <c r="M23" s="3" t="n"/>
-      <c r="O23" s="3" t="n"/>
+      <c r="L23" t="n">
+        <v>22</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0530</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>407.63</v>
+      </c>
       <c r="S23" s="3" t="n"/>
       <c r="T23" s="3" t="n"/>
     </row>
@@ -1667,14 +2019,30 @@
           <t>0545</t>
         </is>
       </c>
-      <c r="D24" s="3" t="n"/>
+      <c r="D24" s="3" t="n">
+        <v>369.79</v>
+      </c>
       <c r="E24" s="3" t="n">
         <v>413.45</v>
       </c>
       <c r="H24" s="3" t="n"/>
       <c r="I24" s="3" t="n"/>
-      <c r="M24" s="3" t="n"/>
-      <c r="O24" s="3" t="n"/>
+      <c r="L24" t="n">
+        <v>23</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0545</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>407.63</v>
+      </c>
       <c r="S24" s="3" t="n"/>
       <c r="T24" s="3" t="n"/>
     </row>
@@ -1692,14 +2060,30 @@
           <t>0600</t>
         </is>
       </c>
-      <c r="D25" s="3" t="n"/>
+      <c r="D25" s="3" t="n">
+        <v>369.79</v>
+      </c>
       <c r="E25" s="3" t="n">
         <v>413.45</v>
       </c>
       <c r="H25" s="3" t="n"/>
       <c r="I25" s="3" t="n"/>
-      <c r="M25" s="3" t="n"/>
-      <c r="O25" s="3" t="n"/>
+      <c r="L25" t="n">
+        <v>24</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0600</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>407.63</v>
+      </c>
       <c r="S25" s="3" t="n"/>
       <c r="T25" s="3" t="n"/>
     </row>
@@ -1717,14 +2101,30 @@
           <t>0615</t>
         </is>
       </c>
-      <c r="D26" s="3" t="n"/>
+      <c r="D26" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E26" s="3" t="n">
         <v>406.41</v>
       </c>
       <c r="H26" s="3" t="n"/>
       <c r="I26" s="3" t="n"/>
-      <c r="M26" s="3" t="n"/>
-      <c r="O26" s="3" t="n"/>
+      <c r="L26" t="n">
+        <v>25</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0615</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>372.69</v>
+      </c>
       <c r="S26" s="3" t="n"/>
       <c r="T26" s="3" t="n"/>
     </row>
@@ -1742,14 +2142,30 @@
           <t>0630</t>
         </is>
       </c>
-      <c r="D27" s="3" t="n"/>
+      <c r="D27" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E27" s="3" t="n">
         <v>403.6</v>
       </c>
       <c r="H27" s="3" t="n"/>
       <c r="I27" s="3" t="n"/>
-      <c r="M27" s="3" t="n"/>
-      <c r="O27" s="3" t="n"/>
+      <c r="L27" t="n">
+        <v>26</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>0630</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>372.69</v>
+      </c>
       <c r="S27" s="3" t="n"/>
       <c r="T27" s="3" t="n"/>
     </row>
@@ -1767,14 +2183,30 @@
           <t>0645</t>
         </is>
       </c>
-      <c r="D28" s="3" t="n"/>
+      <c r="D28" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E28" s="3" t="n">
         <v>404.86</v>
       </c>
       <c r="H28" s="3" t="n"/>
       <c r="I28" s="3" t="n"/>
-      <c r="M28" s="3" t="n"/>
-      <c r="O28" s="3" t="n"/>
+      <c r="L28" t="n">
+        <v>27</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0645</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>372.69</v>
+      </c>
       <c r="S28" s="3" t="n"/>
       <c r="T28" s="3" t="n"/>
     </row>
@@ -1792,14 +2224,30 @@
           <t>0700</t>
         </is>
       </c>
-      <c r="D29" s="3" t="n"/>
+      <c r="D29" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E29" s="3" t="n">
         <v>397.36</v>
       </c>
       <c r="H29" s="3" t="n"/>
       <c r="I29" s="3" t="n"/>
-      <c r="M29" s="3" t="n"/>
-      <c r="O29" s="3" t="n"/>
+      <c r="L29" t="n">
+        <v>28</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0700</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>372.69</v>
+      </c>
       <c r="S29" s="3" t="n"/>
       <c r="T29" s="3" t="n"/>
     </row>
@@ -1817,14 +2265,30 @@
           <t>0715</t>
         </is>
       </c>
-      <c r="D30" s="3" t="n"/>
+      <c r="D30" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E30" s="3" t="n">
         <v>402.5</v>
       </c>
       <c r="H30" s="3" t="n"/>
       <c r="I30" s="3" t="n"/>
-      <c r="M30" s="3" t="n"/>
-      <c r="O30" s="3" t="n"/>
+      <c r="L30" t="n">
+        <v>29</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>0715</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>377.35</v>
+      </c>
       <c r="S30" s="3" t="n"/>
       <c r="T30" s="3" t="n"/>
     </row>
@@ -1842,14 +2306,30 @@
           <t>0730</t>
         </is>
       </c>
-      <c r="D31" s="3" t="n"/>
+      <c r="D31" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E31" s="3" t="n">
         <v>396.39</v>
       </c>
       <c r="H31" s="3" t="n"/>
       <c r="I31" s="3" t="n"/>
-      <c r="M31" s="3" t="n"/>
-      <c r="O31" s="3" t="n"/>
+      <c r="L31" t="n">
+        <v>30</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>0730</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>372.69</v>
+      </c>
       <c r="S31" s="3" t="n"/>
       <c r="T31" s="3" t="n"/>
     </row>
@@ -1867,14 +2347,30 @@
           <t>0745</t>
         </is>
       </c>
-      <c r="D32" s="3" t="n"/>
+      <c r="D32" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E32" s="3" t="n">
         <v>389.26</v>
       </c>
       <c r="H32" s="3" t="n"/>
       <c r="I32" s="3" t="n"/>
-      <c r="M32" s="3" t="n"/>
-      <c r="O32" s="3" t="n"/>
+      <c r="L32" t="n">
+        <v>31</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0745</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>372.69</v>
+      </c>
       <c r="S32" s="3" t="n"/>
       <c r="T32" s="3" t="n"/>
     </row>
@@ -1892,14 +2388,30 @@
           <t>0800</t>
         </is>
       </c>
-      <c r="D33" s="3" t="n"/>
+      <c r="D33" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E33" s="3" t="n">
         <v>381.01</v>
       </c>
       <c r="H33" s="3" t="n"/>
       <c r="I33" s="3" t="n"/>
-      <c r="M33" s="3" t="n"/>
-      <c r="O33" s="3" t="n"/>
+      <c r="L33" t="n">
+        <v>32</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>0800</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>372.69</v>
+      </c>
       <c r="S33" s="3" t="n"/>
       <c r="T33" s="3" t="n"/>
     </row>
@@ -1917,14 +2429,30 @@
           <t>0815</t>
         </is>
       </c>
-      <c r="D34" s="3" t="n"/>
+      <c r="D34" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E34" s="3" t="n">
         <v>379.47</v>
       </c>
       <c r="H34" s="3" t="n"/>
       <c r="I34" s="3" t="n"/>
-      <c r="M34" s="3" t="n"/>
-      <c r="O34" s="3" t="n"/>
+      <c r="L34" t="n">
+        <v>33</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0815</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>362</v>
+      </c>
       <c r="S34" s="3" t="n"/>
       <c r="T34" s="3" t="n"/>
     </row>
@@ -1942,14 +2470,30 @@
           <t>0830</t>
         </is>
       </c>
-      <c r="D35" s="3" t="n"/>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E35" s="3" t="n">
         <v>371.14</v>
       </c>
       <c r="H35" s="3" t="n"/>
       <c r="I35" s="3" t="n"/>
-      <c r="M35" s="3" t="n"/>
-      <c r="O35" s="3" t="n"/>
+      <c r="L35" t="n">
+        <v>34</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>0830</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>367.23</v>
+      </c>
       <c r="S35" s="3" t="n"/>
       <c r="T35" s="3" t="n"/>
     </row>
@@ -1967,14 +2511,30 @@
           <t>0845</t>
         </is>
       </c>
-      <c r="D36" s="3" t="n"/>
+      <c r="D36" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E36" s="3" t="n">
         <v>357.01</v>
       </c>
       <c r="H36" s="3" t="n"/>
       <c r="I36" s="3" t="n"/>
-      <c r="M36" s="3" t="n"/>
-      <c r="O36" s="3" t="n"/>
+      <c r="L36" t="n">
+        <v>35</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>0845</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="n">
+        <v>367.23</v>
+      </c>
       <c r="S36" s="3" t="n"/>
       <c r="T36" s="3" t="n"/>
     </row>
@@ -1992,14 +2552,30 @@
           <t>0900</t>
         </is>
       </c>
-      <c r="D37" s="3" t="n"/>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E37" s="3" t="n">
         <v>348.76</v>
       </c>
       <c r="H37" s="3" t="n"/>
       <c r="I37" s="3" t="n"/>
-      <c r="M37" s="3" t="n"/>
-      <c r="O37" s="3" t="n"/>
+      <c r="L37" t="n">
+        <v>36</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0900</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="n">
+        <v>365.04</v>
+      </c>
       <c r="S37" s="3" t="n"/>
       <c r="T37" s="3" t="n"/>
     </row>
@@ -2017,14 +2593,30 @@
           <t>0915</t>
         </is>
       </c>
-      <c r="D38" s="3" t="n"/>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E38" s="3" t="n">
         <v>348.42</v>
       </c>
       <c r="H38" s="3" t="n"/>
       <c r="I38" s="3" t="n"/>
-      <c r="M38" s="3" t="n"/>
-      <c r="O38" s="3" t="n"/>
+      <c r="L38" t="n">
+        <v>37</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0915</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="n">
+        <v>362</v>
+      </c>
       <c r="S38" s="3" t="n"/>
       <c r="T38" s="3" t="n"/>
     </row>
@@ -2042,14 +2634,30 @@
           <t>0930</t>
         </is>
       </c>
-      <c r="D39" s="3" t="n"/>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E39" s="3" t="n">
         <v>349.05</v>
       </c>
       <c r="H39" s="3" t="n"/>
       <c r="I39" s="3" t="n"/>
-      <c r="M39" s="3" t="n"/>
-      <c r="O39" s="3" t="n"/>
+      <c r="L39" t="n">
+        <v>38</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0930</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="n">
+        <v>390.27</v>
+      </c>
       <c r="S39" s="3" t="n"/>
       <c r="T39" s="3" t="n"/>
     </row>
@@ -2067,14 +2675,30 @@
           <t>0945</t>
         </is>
       </c>
-      <c r="D40" s="3" t="n"/>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E40" s="3" t="n">
         <v>350</v>
       </c>
       <c r="H40" s="3" t="n"/>
       <c r="I40" s="3" t="n"/>
-      <c r="M40" s="3" t="n"/>
-      <c r="O40" s="3" t="n"/>
+      <c r="L40" t="n">
+        <v>39</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0945</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="n">
+        <v>362</v>
+      </c>
       <c r="S40" s="3" t="n"/>
       <c r="T40" s="3" t="n"/>
     </row>
@@ -2092,14 +2716,30 @@
           <t>1000</t>
         </is>
       </c>
-      <c r="D41" s="3" t="n"/>
+      <c r="D41" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E41" s="3" t="n">
         <v>349.33</v>
       </c>
       <c r="H41" s="3" t="n"/>
       <c r="I41" s="3" t="n"/>
-      <c r="M41" s="3" t="n"/>
-      <c r="O41" s="3" t="n"/>
+      <c r="L41" t="n">
+        <v>40</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>362</v>
+      </c>
       <c r="S41" s="3" t="n"/>
       <c r="T41" s="3" t="n"/>
     </row>
@@ -2117,14 +2757,30 @@
           <t>1015</t>
         </is>
       </c>
-      <c r="D42" s="3" t="n"/>
+      <c r="D42" s="3" t="n">
+        <v>330.44</v>
+      </c>
       <c r="E42" s="3" t="n">
         <v>349.54</v>
       </c>
       <c r="H42" s="3" t="n"/>
       <c r="I42" s="3" t="n"/>
-      <c r="M42" s="3" t="n"/>
-      <c r="O42" s="3" t="n"/>
+      <c r="L42" t="n">
+        <v>41</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="n">
+        <v>316.98</v>
+      </c>
       <c r="S42" s="3" t="n"/>
       <c r="T42" s="3" t="n"/>
     </row>
@@ -2142,14 +2798,30 @@
           <t>1030</t>
         </is>
       </c>
-      <c r="D43" s="3" t="n"/>
+      <c r="D43" s="3" t="n">
+        <v>330.44</v>
+      </c>
       <c r="E43" s="3" t="n">
         <v>348.85</v>
       </c>
       <c r="H43" s="3" t="n"/>
       <c r="I43" s="3" t="n"/>
-      <c r="M43" s="3" t="n"/>
-      <c r="O43" s="3" t="n"/>
+      <c r="L43" t="n">
+        <v>42</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="n">
+        <v>316.98</v>
+      </c>
       <c r="S43" s="3" t="n"/>
       <c r="T43" s="3" t="n"/>
     </row>
@@ -2167,14 +2839,30 @@
           <t>1045</t>
         </is>
       </c>
-      <c r="D44" s="3" t="n"/>
+      <c r="D44" s="3" t="n">
+        <v>330.44</v>
+      </c>
       <c r="E44" s="3" t="n">
         <v>346.39</v>
       </c>
       <c r="H44" s="3" t="n"/>
       <c r="I44" s="3" t="n"/>
-      <c r="M44" s="3" t="n"/>
-      <c r="O44" s="3" t="n"/>
+      <c r="L44" t="n">
+        <v>43</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1045</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="n">
+        <v>316.98</v>
+      </c>
       <c r="S44" s="3" t="n"/>
       <c r="T44" s="3" t="n"/>
     </row>
@@ -2192,14 +2880,30 @@
           <t>1100</t>
         </is>
       </c>
-      <c r="D45" s="3" t="n"/>
+      <c r="D45" s="3" t="n">
+        <v>330.44</v>
+      </c>
       <c r="E45" s="3" t="n">
         <v>350</v>
       </c>
       <c r="H45" s="3" t="n"/>
       <c r="I45" s="3" t="n"/>
-      <c r="M45" s="3" t="n"/>
-      <c r="O45" s="3" t="n"/>
+      <c r="L45" t="n">
+        <v>44</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>316.98</v>
+      </c>
       <c r="S45" s="3" t="n"/>
       <c r="T45" s="3" t="n"/>
     </row>
@@ -2217,14 +2921,30 @@
           <t>1115</t>
         </is>
       </c>
-      <c r="D46" s="3" t="n"/>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E46" s="3" t="n">
         <v>349.33</v>
       </c>
       <c r="H46" s="3" t="n"/>
       <c r="I46" s="3" t="n"/>
-      <c r="M46" s="3" t="n"/>
-      <c r="O46" s="3" t="n"/>
+      <c r="L46" t="n">
+        <v>45</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>1115</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="S46" s="3" t="n"/>
       <c r="T46" s="3" t="n"/>
     </row>
@@ -2242,14 +2962,30 @@
           <t>1130</t>
         </is>
       </c>
-      <c r="D47" s="3" t="n"/>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E47" s="3" t="n">
         <v>430.32</v>
       </c>
       <c r="H47" s="3" t="n"/>
       <c r="I47" s="3" t="n"/>
-      <c r="M47" s="3" t="n"/>
-      <c r="O47" s="3" t="n"/>
+      <c r="L47" t="n">
+        <v>46</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>1130</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="S47" s="3" t="n"/>
       <c r="T47" s="3" t="n"/>
     </row>
@@ -2267,14 +3003,30 @@
           <t>1145</t>
         </is>
       </c>
-      <c r="D48" s="3" t="n"/>
+      <c r="D48" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E48" s="3" t="n">
         <v>365.5</v>
       </c>
       <c r="H48" s="3" t="n"/>
       <c r="I48" s="3" t="n"/>
-      <c r="M48" s="3" t="n"/>
-      <c r="O48" s="3" t="n"/>
+      <c r="L48" t="n">
+        <v>47</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>1145</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="S48" s="3" t="n"/>
       <c r="T48" s="3" t="n"/>
     </row>
@@ -2292,14 +3044,30 @@
           <t>1200</t>
         </is>
       </c>
-      <c r="D49" s="3" t="n"/>
+      <c r="D49" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E49" s="3" t="n">
         <v>348.76</v>
       </c>
       <c r="H49" s="3" t="n"/>
       <c r="I49" s="3" t="n"/>
-      <c r="M49" s="3" t="n"/>
-      <c r="O49" s="3" t="n"/>
+      <c r="L49" t="n">
+        <v>48</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>1200</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="S49" s="3" t="n"/>
       <c r="T49" s="3" t="n"/>
     </row>
@@ -2317,14 +3085,30 @@
           <t>1215</t>
         </is>
       </c>
-      <c r="D50" s="3" t="n"/>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E50" s="3" t="n">
         <v>343.01</v>
       </c>
       <c r="H50" s="3" t="n"/>
       <c r="I50" s="3" t="n"/>
-      <c r="M50" s="3" t="n"/>
-      <c r="O50" s="3" t="n"/>
+      <c r="L50" t="n">
+        <v>49</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="S50" s="3" t="n"/>
       <c r="T50" s="3" t="n"/>
     </row>
@@ -2342,14 +3126,30 @@
           <t>1230</t>
         </is>
       </c>
-      <c r="D51" s="3" t="n"/>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E51" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H51" s="3" t="n"/>
       <c r="I51" s="3" t="n"/>
-      <c r="M51" s="3" t="n"/>
-      <c r="O51" s="3" t="n"/>
+      <c r="L51" t="n">
+        <v>50</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>1230</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="S51" s="3" t="n"/>
       <c r="T51" s="3" t="n"/>
     </row>
@@ -2367,14 +3167,30 @@
           <t>1245</t>
         </is>
       </c>
-      <c r="D52" s="3" t="n"/>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E52" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H52" s="3" t="n"/>
       <c r="I52" s="3" t="n"/>
-      <c r="M52" s="3" t="n"/>
-      <c r="O52" s="3" t="n"/>
+      <c r="L52" t="n">
+        <v>51</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>1245</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="S52" s="3" t="n"/>
       <c r="T52" s="3" t="n"/>
     </row>
@@ -2392,14 +3208,30 @@
           <t>1300</t>
         </is>
       </c>
-      <c r="D53" s="3" t="n"/>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E53" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H53" s="3" t="n"/>
       <c r="I53" s="3" t="n"/>
-      <c r="M53" s="3" t="n"/>
-      <c r="O53" s="3" t="n"/>
+      <c r="L53" t="n">
+        <v>52</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1300</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="S53" s="3" t="n"/>
       <c r="T53" s="3" t="n"/>
     </row>
@@ -2417,14 +3249,30 @@
           <t>1315</t>
         </is>
       </c>
-      <c r="D54" s="3" t="n"/>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E54" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H54" s="3" t="n"/>
       <c r="I54" s="3" t="n"/>
-      <c r="M54" s="3" t="n"/>
-      <c r="O54" s="3" t="n"/>
+      <c r="L54" t="n">
+        <v>53</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>1315</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="S54" s="3" t="n"/>
       <c r="T54" s="3" t="n"/>
     </row>
@@ -2442,14 +3290,30 @@
           <t>1330</t>
         </is>
       </c>
-      <c r="D55" s="3" t="n"/>
+      <c r="D55" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E55" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H55" s="3" t="n"/>
       <c r="I55" s="3" t="n"/>
-      <c r="M55" s="3" t="n"/>
-      <c r="O55" s="3" t="n"/>
+      <c r="L55" t="n">
+        <v>54</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>1330</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="S55" s="3" t="n"/>
       <c r="T55" s="3" t="n"/>
     </row>
@@ -2467,14 +3331,30 @@
           <t>1345</t>
         </is>
       </c>
-      <c r="D56" s="3" t="n"/>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E56" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H56" s="3" t="n"/>
       <c r="I56" s="3" t="n"/>
-      <c r="M56" s="3" t="n"/>
-      <c r="O56" s="3" t="n"/>
+      <c r="L56" t="n">
+        <v>55</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>1345</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="S56" s="3" t="n"/>
       <c r="T56" s="3" t="n"/>
     </row>
@@ -2492,14 +3372,30 @@
           <t>1400</t>
         </is>
       </c>
-      <c r="D57" s="3" t="n"/>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E57" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H57" s="3" t="n"/>
       <c r="I57" s="3" t="n"/>
-      <c r="M57" s="3" t="n"/>
-      <c r="O57" s="3" t="n"/>
+      <c r="L57" t="n">
+        <v>56</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>1400</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="S57" s="3" t="n"/>
       <c r="T57" s="3" t="n"/>
     </row>
@@ -2517,14 +3413,30 @@
           <t>1415</t>
         </is>
       </c>
-      <c r="D58" s="3" t="n"/>
+      <c r="D58" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E58" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H58" s="3" t="n"/>
       <c r="I58" s="3" t="n"/>
-      <c r="M58" s="3" t="n"/>
-      <c r="O58" s="3" t="n"/>
+      <c r="L58" t="n">
+        <v>57</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>1415</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="S58" s="3" t="n"/>
       <c r="T58" s="3" t="n"/>
     </row>
@@ -2542,14 +3454,30 @@
           <t>1430</t>
         </is>
       </c>
-      <c r="D59" s="3" t="n"/>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E59" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H59" s="3" t="n"/>
       <c r="I59" s="3" t="n"/>
-      <c r="M59" s="3" t="n"/>
-      <c r="O59" s="3" t="n"/>
+      <c r="L59" t="n">
+        <v>58</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>1430</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="S59" s="3" t="n"/>
       <c r="T59" s="3" t="n"/>
     </row>
@@ -2567,14 +3495,30 @@
           <t>1445</t>
         </is>
       </c>
-      <c r="D60" s="3" t="n"/>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E60" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H60" s="3" t="n"/>
       <c r="I60" s="3" t="n"/>
-      <c r="M60" s="3" t="n"/>
-      <c r="O60" s="3" t="n"/>
+      <c r="L60" t="n">
+        <v>59</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>1445</t>
+        </is>
+      </c>
+      <c r="O60" s="3" t="n">
+        <v>362</v>
+      </c>
       <c r="S60" s="3" t="n"/>
       <c r="T60" s="3" t="n"/>
     </row>
@@ -2592,14 +3536,30 @@
           <t>1500</t>
         </is>
       </c>
-      <c r="D61" s="3" t="n"/>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E61" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H61" s="3" t="n"/>
       <c r="I61" s="3" t="n"/>
-      <c r="M61" s="3" t="n"/>
-      <c r="O61" s="3" t="n"/>
+      <c r="L61" t="n">
+        <v>60</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="O61" s="3" t="n">
+        <v>362</v>
+      </c>
       <c r="S61" s="3" t="n"/>
       <c r="T61" s="3" t="n"/>
     </row>
@@ -2617,14 +3577,30 @@
           <t>1515</t>
         </is>
       </c>
-      <c r="D62" s="3" t="n"/>
+      <c r="D62" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E62" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H62" s="3" t="n"/>
       <c r="I62" s="3" t="n"/>
-      <c r="M62" s="3" t="n"/>
-      <c r="O62" s="3" t="n"/>
+      <c r="L62" t="n">
+        <v>61</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>1515</t>
+        </is>
+      </c>
+      <c r="O62" s="3" t="n">
+        <v>211.55</v>
+      </c>
       <c r="S62" s="3" t="n"/>
       <c r="T62" s="3" t="n"/>
     </row>
@@ -2642,14 +3618,30 @@
           <t>1530</t>
         </is>
       </c>
-      <c r="D63" s="3" t="n"/>
+      <c r="D63" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E63" s="3" t="n">
         <v>348.76</v>
       </c>
       <c r="H63" s="3" t="n"/>
       <c r="I63" s="3" t="n"/>
-      <c r="M63" s="3" t="n"/>
-      <c r="O63" s="3" t="n"/>
+      <c r="L63" t="n">
+        <v>62</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>1530</t>
+        </is>
+      </c>
+      <c r="O63" s="3" t="n">
+        <v>211.55</v>
+      </c>
       <c r="S63" s="3" t="n"/>
       <c r="T63" s="3" t="n"/>
     </row>
@@ -2667,14 +3659,30 @@
           <t>1545</t>
         </is>
       </c>
-      <c r="D64" s="3" t="n"/>
+      <c r="D64" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E64" s="3" t="n">
         <v>198.32</v>
       </c>
       <c r="H64" s="3" t="n"/>
       <c r="I64" s="3" t="n"/>
-      <c r="M64" s="3" t="n"/>
-      <c r="O64" s="3" t="n"/>
+      <c r="L64" t="n">
+        <v>63</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>1545</t>
+        </is>
+      </c>
+      <c r="O64" s="3" t="n">
+        <v>211.55</v>
+      </c>
       <c r="S64" s="3" t="n"/>
       <c r="T64" s="3" t="n"/>
     </row>
@@ -2692,14 +3700,30 @@
           <t>1600</t>
         </is>
       </c>
-      <c r="D65" s="3" t="n"/>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="E65" s="3" t="n">
         <v>198.32</v>
       </c>
       <c r="H65" s="3" t="n"/>
       <c r="I65" s="3" t="n"/>
-      <c r="M65" s="3" t="n"/>
-      <c r="O65" s="3" t="n"/>
+      <c r="L65" t="n">
+        <v>64</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="O65" s="3" t="n">
+        <v>211.55</v>
+      </c>
       <c r="S65" s="3" t="n"/>
       <c r="T65" s="3" t="n"/>
     </row>
@@ -2717,14 +3741,30 @@
           <t>1615</t>
         </is>
       </c>
-      <c r="D66" s="3" t="n"/>
+      <c r="D66" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E66" s="3" t="n">
         <v>364.61</v>
       </c>
       <c r="H66" s="3" t="n"/>
       <c r="I66" s="3" t="n"/>
-      <c r="M66" s="3" t="n"/>
-      <c r="O66" s="3" t="n"/>
+      <c r="L66" t="n">
+        <v>65</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>1615</t>
+        </is>
+      </c>
+      <c r="O66" s="3" t="n">
+        <v>402.57</v>
+      </c>
       <c r="S66" s="3" t="n"/>
       <c r="T66" s="3" t="n"/>
     </row>
@@ -2742,14 +3782,30 @@
           <t>1630</t>
         </is>
       </c>
-      <c r="D67" s="3" t="n"/>
+      <c r="D67" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E67" s="3" t="n">
         <v>373.77</v>
       </c>
       <c r="H67" s="3" t="n"/>
       <c r="I67" s="3" t="n"/>
-      <c r="M67" s="3" t="n"/>
-      <c r="O67" s="3" t="n"/>
+      <c r="L67" t="n">
+        <v>66</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>1630</t>
+        </is>
+      </c>
+      <c r="O67" s="3" t="n">
+        <v>402.57</v>
+      </c>
       <c r="S67" s="3" t="n"/>
       <c r="T67" s="3" t="n"/>
     </row>
@@ -2767,14 +3823,30 @@
           <t>1645</t>
         </is>
       </c>
-      <c r="D68" s="3" t="n"/>
+      <c r="D68" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E68" s="3" t="n">
         <v>380.07</v>
       </c>
       <c r="H68" s="3" t="n"/>
       <c r="I68" s="3" t="n"/>
-      <c r="M68" s="3" t="n"/>
-      <c r="O68" s="3" t="n"/>
+      <c r="L68" t="n">
+        <v>67</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>1645</t>
+        </is>
+      </c>
+      <c r="O68" s="3" t="n">
+        <v>402.57</v>
+      </c>
       <c r="S68" s="3" t="n"/>
       <c r="T68" s="3" t="n"/>
     </row>
@@ -2792,14 +3864,30 @@
           <t>1700</t>
         </is>
       </c>
-      <c r="D69" s="3" t="n"/>
+      <c r="D69" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E69" s="3" t="n">
         <v>387.14</v>
       </c>
       <c r="H69" s="3" t="n"/>
       <c r="I69" s="3" t="n"/>
-      <c r="M69" s="3" t="n"/>
-      <c r="O69" s="3" t="n"/>
+      <c r="L69" t="n">
+        <v>68</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>1700</t>
+        </is>
+      </c>
+      <c r="O69" s="3" t="n">
+        <v>402.57</v>
+      </c>
       <c r="S69" s="3" t="n"/>
       <c r="T69" s="3" t="n"/>
     </row>
@@ -2817,14 +3905,30 @@
           <t>1715</t>
         </is>
       </c>
-      <c r="D70" s="3" t="n"/>
+      <c r="D70" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E70" s="3" t="n">
         <v>410.83</v>
       </c>
       <c r="H70" s="3" t="n"/>
       <c r="I70" s="3" t="n"/>
-      <c r="M70" s="3" t="n"/>
-      <c r="O70" s="3" t="n"/>
+      <c r="L70" t="n">
+        <v>69</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>1715</t>
+        </is>
+      </c>
+      <c r="O70" s="3" t="n">
+        <v>402.57</v>
+      </c>
       <c r="S70" s="3" t="n"/>
       <c r="T70" s="3" t="n"/>
     </row>
@@ -2842,14 +3946,30 @@
           <t>1730</t>
         </is>
       </c>
-      <c r="D71" s="3" t="n"/>
+      <c r="D71" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E71" s="3" t="n">
         <v>413.32</v>
       </c>
       <c r="H71" s="3" t="n"/>
       <c r="I71" s="3" t="n"/>
-      <c r="M71" s="3" t="n"/>
-      <c r="O71" s="3" t="n"/>
+      <c r="L71" t="n">
+        <v>70</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>1730</t>
+        </is>
+      </c>
+      <c r="O71" s="3" t="n">
+        <v>402.57</v>
+      </c>
       <c r="S71" s="3" t="n"/>
       <c r="T71" s="3" t="n"/>
     </row>
@@ -2867,14 +3987,30 @@
           <t>1745</t>
         </is>
       </c>
-      <c r="D72" s="3" t="n"/>
+      <c r="D72" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E72" s="3" t="n">
         <v>420.5</v>
       </c>
       <c r="H72" s="3" t="n"/>
       <c r="I72" s="3" t="n"/>
-      <c r="M72" s="3" t="n"/>
-      <c r="O72" s="3" t="n"/>
+      <c r="L72" t="n">
+        <v>71</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>1745</t>
+        </is>
+      </c>
+      <c r="O72" s="3" t="n">
+        <v>402.57</v>
+      </c>
       <c r="S72" s="3" t="n"/>
       <c r="T72" s="3" t="n"/>
     </row>
@@ -2892,14 +4028,30 @@
           <t>1800</t>
         </is>
       </c>
-      <c r="D73" s="3" t="n"/>
+      <c r="D73" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E73" s="3" t="n">
         <v>421.58</v>
       </c>
       <c r="H73" s="3" t="n"/>
       <c r="I73" s="3" t="n"/>
-      <c r="M73" s="3" t="n"/>
-      <c r="O73" s="3" t="n"/>
+      <c r="L73" t="n">
+        <v>72</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="O73" s="3" t="n">
+        <v>402.57</v>
+      </c>
       <c r="S73" s="3" t="n"/>
       <c r="T73" s="3" t="n"/>
     </row>
@@ -2917,14 +4069,30 @@
           <t>1815</t>
         </is>
       </c>
-      <c r="D74" s="3" t="n"/>
+      <c r="D74" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E74" s="3" t="n">
         <v>413.94</v>
       </c>
       <c r="H74" s="3" t="n"/>
       <c r="I74" s="3" t="n"/>
-      <c r="M74" s="3" t="n"/>
-      <c r="O74" s="3" t="n"/>
+      <c r="L74" t="n">
+        <v>73</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>1815</t>
+        </is>
+      </c>
+      <c r="O74" s="3" t="n">
+        <v>407.63</v>
+      </c>
       <c r="S74" s="3" t="n"/>
       <c r="T74" s="3" t="n"/>
     </row>
@@ -2942,14 +4110,30 @@
           <t>1830</t>
         </is>
       </c>
-      <c r="D75" s="3" t="n"/>
+      <c r="D75" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E75" s="3" t="n">
         <v>421.1</v>
       </c>
       <c r="H75" s="3" t="n"/>
       <c r="I75" s="3" t="n"/>
-      <c r="M75" s="3" t="n"/>
-      <c r="O75" s="3" t="n"/>
+      <c r="L75" t="n">
+        <v>74</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>1830</t>
+        </is>
+      </c>
+      <c r="O75" s="3" t="n">
+        <v>407.63</v>
+      </c>
       <c r="S75" s="3" t="n"/>
       <c r="T75" s="3" t="n"/>
     </row>
@@ -2967,14 +4151,30 @@
           <t>1845</t>
         </is>
       </c>
-      <c r="D76" s="3" t="n"/>
+      <c r="D76" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E76" s="3" t="n">
         <v>420.5</v>
       </c>
       <c r="H76" s="3" t="n"/>
       <c r="I76" s="3" t="n"/>
-      <c r="M76" s="3" t="n"/>
-      <c r="O76" s="3" t="n"/>
+      <c r="L76" t="n">
+        <v>75</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>1845</t>
+        </is>
+      </c>
+      <c r="O76" s="3" t="n">
+        <v>407.63</v>
+      </c>
       <c r="S76" s="3" t="n"/>
       <c r="T76" s="3" t="n"/>
     </row>
@@ -2992,14 +4192,30 @@
           <t>1900</t>
         </is>
       </c>
-      <c r="D77" s="3" t="n"/>
+      <c r="D77" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E77" s="3" t="n">
         <v>413.64</v>
       </c>
       <c r="H77" s="3" t="n"/>
       <c r="I77" s="3" t="n"/>
-      <c r="M77" s="3" t="n"/>
-      <c r="O77" s="3" t="n"/>
+      <c r="L77" t="n">
+        <v>76</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>1900</t>
+        </is>
+      </c>
+      <c r="O77" s="3" t="n">
+        <v>407.63</v>
+      </c>
       <c r="S77" s="3" t="n"/>
       <c r="T77" s="3" t="n"/>
     </row>
@@ -3017,14 +4233,30 @@
           <t>1915</t>
         </is>
       </c>
-      <c r="D78" s="3" t="n"/>
+      <c r="D78" s="3" t="n">
+        <v>369.79</v>
+      </c>
       <c r="E78" s="3" t="n">
         <v>421.89</v>
       </c>
       <c r="H78" s="3" t="n"/>
       <c r="I78" s="3" t="n"/>
-      <c r="M78" s="3" t="n"/>
-      <c r="O78" s="3" t="n"/>
+      <c r="L78" t="n">
+        <v>77</v>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>1915</t>
+        </is>
+      </c>
+      <c r="O78" s="3" t="n">
+        <v>399.01</v>
+      </c>
       <c r="S78" s="3" t="n"/>
       <c r="T78" s="3" t="n"/>
     </row>
@@ -3042,14 +4274,30 @@
           <t>1930</t>
         </is>
       </c>
-      <c r="D79" s="3" t="n"/>
+      <c r="D79" s="3" t="n">
+        <v>369.79</v>
+      </c>
       <c r="E79" s="3" t="n">
         <v>417.16</v>
       </c>
       <c r="H79" s="3" t="n"/>
       <c r="I79" s="3" t="n"/>
-      <c r="M79" s="3" t="n"/>
-      <c r="O79" s="3" t="n"/>
+      <c r="L79" t="n">
+        <v>78</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>1930</t>
+        </is>
+      </c>
+      <c r="O79" s="3" t="n">
+        <v>399.01</v>
+      </c>
       <c r="S79" s="3" t="n"/>
       <c r="T79" s="3" t="n"/>
     </row>
@@ -3067,14 +4315,30 @@
           <t>1945</t>
         </is>
       </c>
-      <c r="D80" s="3" t="n"/>
+      <c r="D80" s="3" t="n">
+        <v>369.79</v>
+      </c>
       <c r="E80" s="3" t="n">
         <v>402.85</v>
       </c>
       <c r="H80" s="3" t="n"/>
       <c r="I80" s="3" t="n"/>
-      <c r="M80" s="3" t="n"/>
-      <c r="O80" s="3" t="n"/>
+      <c r="L80" t="n">
+        <v>79</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>1945</t>
+        </is>
+      </c>
+      <c r="O80" s="3" t="n">
+        <v>399.01</v>
+      </c>
       <c r="S80" s="3" t="n"/>
       <c r="T80" s="3" t="n"/>
     </row>
@@ -3092,14 +4356,30 @@
           <t>2000</t>
         </is>
       </c>
-      <c r="D81" s="3" t="n"/>
+      <c r="D81" s="3" t="n">
+        <v>361.85</v>
+      </c>
       <c r="E81" s="3" t="n">
         <v>403.35</v>
       </c>
       <c r="H81" s="3" t="n"/>
       <c r="I81" s="3" t="n"/>
-      <c r="M81" s="3" t="n"/>
-      <c r="O81" s="3" t="n"/>
+      <c r="L81" t="n">
+        <v>80</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="O81" s="3" t="n">
+        <v>399.01</v>
+      </c>
       <c r="S81" s="3" t="n"/>
       <c r="T81" s="3" t="n"/>
     </row>
@@ -3117,14 +4397,30 @@
           <t>2015</t>
         </is>
       </c>
-      <c r="D82" s="3" t="n"/>
+      <c r="D82" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E82" s="3" t="n">
         <v>409.55</v>
       </c>
       <c r="H82" s="3" t="n"/>
       <c r="I82" s="3" t="n"/>
-      <c r="M82" s="3" t="n"/>
-      <c r="O82" s="3" t="n"/>
+      <c r="L82" t="n">
+        <v>81</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="O82" s="3" t="n">
+        <v>399.01</v>
+      </c>
       <c r="S82" s="3" t="n"/>
       <c r="T82" s="3" t="n"/>
     </row>
@@ -3142,14 +4438,30 @@
           <t>2030</t>
         </is>
       </c>
-      <c r="D83" s="3" t="n"/>
+      <c r="D83" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E83" s="3" t="n">
         <v>404.29</v>
       </c>
       <c r="H83" s="3" t="n"/>
       <c r="I83" s="3" t="n"/>
-      <c r="M83" s="3" t="n"/>
-      <c r="O83" s="3" t="n"/>
+      <c r="L83" t="n">
+        <v>82</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="O83" s="3" t="n">
+        <v>399.01</v>
+      </c>
       <c r="S83" s="3" t="n"/>
       <c r="T83" s="3" t="n"/>
     </row>
@@ -3167,14 +4479,30 @@
           <t>2045</t>
         </is>
       </c>
-      <c r="D84" s="3" t="n"/>
+      <c r="D84" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E84" s="3" t="n">
         <v>397.66</v>
       </c>
       <c r="H84" s="3" t="n"/>
       <c r="I84" s="3" t="n"/>
-      <c r="M84" s="3" t="n"/>
-      <c r="O84" s="3" t="n"/>
+      <c r="L84" t="n">
+        <v>83</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>2045</t>
+        </is>
+      </c>
+      <c r="O84" s="3" t="n">
+        <v>399.01</v>
+      </c>
       <c r="S84" s="3" t="n"/>
       <c r="T84" s="3" t="n"/>
     </row>
@@ -3192,14 +4520,30 @@
           <t>2100</t>
         </is>
       </c>
-      <c r="D85" s="3" t="n"/>
+      <c r="D85" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E85" s="3" t="n">
         <v>396.22</v>
       </c>
       <c r="H85" s="3" t="n"/>
       <c r="I85" s="3" t="n"/>
-      <c r="M85" s="3" t="n"/>
-      <c r="O85" s="3" t="n"/>
+      <c r="L85" t="n">
+        <v>84</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>2100</t>
+        </is>
+      </c>
+      <c r="O85" s="3" t="n">
+        <v>399.01</v>
+      </c>
       <c r="S85" s="3" t="n"/>
       <c r="T85" s="3" t="n"/>
     </row>
@@ -3217,14 +4561,30 @@
           <t>2115</t>
         </is>
       </c>
-      <c r="D86" s="3" t="n"/>
+      <c r="D86" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E86" s="3" t="n">
         <v>397.66</v>
       </c>
       <c r="H86" s="3" t="n"/>
       <c r="I86" s="3" t="n"/>
-      <c r="M86" s="3" t="n"/>
-      <c r="O86" s="3" t="n"/>
+      <c r="L86" t="n">
+        <v>85</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>2115</t>
+        </is>
+      </c>
+      <c r="O86" s="3" t="n">
+        <v>397.17</v>
+      </c>
       <c r="S86" s="3" t="n"/>
       <c r="T86" s="3" t="n"/>
     </row>
@@ -3242,14 +4602,30 @@
           <t>2130</t>
         </is>
       </c>
-      <c r="D87" s="3" t="n"/>
+      <c r="D87" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E87" s="3" t="n">
         <v>397.58</v>
       </c>
       <c r="H87" s="3" t="n"/>
       <c r="I87" s="3" t="n"/>
-      <c r="M87" s="3" t="n"/>
-      <c r="O87" s="3" t="n"/>
+      <c r="L87" t="n">
+        <v>86</v>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>2130</t>
+        </is>
+      </c>
+      <c r="O87" s="3" t="n">
+        <v>397.17</v>
+      </c>
       <c r="S87" s="3" t="n"/>
       <c r="T87" s="3" t="n"/>
     </row>
@@ -3267,14 +4643,30 @@
           <t>2145</t>
         </is>
       </c>
-      <c r="D88" s="3" t="n"/>
+      <c r="D88" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E88" s="3" t="n">
         <v>398.85</v>
       </c>
       <c r="H88" s="3" t="n"/>
       <c r="I88" s="3" t="n"/>
-      <c r="M88" s="3" t="n"/>
-      <c r="O88" s="3" t="n"/>
+      <c r="L88" t="n">
+        <v>87</v>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>2145</t>
+        </is>
+      </c>
+      <c r="O88" s="3" t="n">
+        <v>397.17</v>
+      </c>
       <c r="S88" s="3" t="n"/>
       <c r="T88" s="3" t="n"/>
     </row>
@@ -3292,14 +4684,30 @@
           <t>2200</t>
         </is>
       </c>
-      <c r="D89" s="3" t="n"/>
+      <c r="D89" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E89" s="3" t="n">
         <v>396.55</v>
       </c>
       <c r="H89" s="3" t="n"/>
       <c r="I89" s="3" t="n"/>
-      <c r="M89" s="3" t="n"/>
-      <c r="O89" s="3" t="n"/>
+      <c r="L89" t="n">
+        <v>88</v>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>2200</t>
+        </is>
+      </c>
+      <c r="O89" s="3" t="n">
+        <v>397.17</v>
+      </c>
       <c r="S89" s="3" t="n"/>
       <c r="T89" s="3" t="n"/>
     </row>
@@ -3317,14 +4725,30 @@
           <t>2215</t>
         </is>
       </c>
-      <c r="D90" s="3" t="n"/>
+      <c r="D90" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E90" s="3" t="n">
         <v>403.22</v>
       </c>
       <c r="H90" s="3" t="n"/>
       <c r="I90" s="3" t="n"/>
-      <c r="M90" s="3" t="n"/>
-      <c r="O90" s="3" t="n"/>
+      <c r="L90" t="n">
+        <v>89</v>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>2215</t>
+        </is>
+      </c>
+      <c r="O90" s="3" t="n">
+        <v>397.17</v>
+      </c>
       <c r="S90" s="3" t="n"/>
       <c r="T90" s="3" t="n"/>
     </row>
@@ -3342,14 +4766,30 @@
           <t>2230</t>
         </is>
       </c>
-      <c r="D91" s="3" t="n"/>
+      <c r="D91" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E91" s="3" t="n">
         <v>404.29</v>
       </c>
       <c r="H91" s="3" t="n"/>
       <c r="I91" s="3" t="n"/>
-      <c r="M91" s="3" t="n"/>
-      <c r="O91" s="3" t="n"/>
+      <c r="L91" t="n">
+        <v>90</v>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>2230</t>
+        </is>
+      </c>
+      <c r="O91" s="3" t="n">
+        <v>397.17</v>
+      </c>
       <c r="S91" s="3" t="n"/>
       <c r="T91" s="3" t="n"/>
     </row>
@@ -3367,14 +4807,30 @@
           <t>2245</t>
         </is>
       </c>
-      <c r="D92" s="3" t="n"/>
+      <c r="D92" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E92" s="3" t="n">
         <v>406.41</v>
       </c>
       <c r="H92" s="3" t="n"/>
       <c r="I92" s="3" t="n"/>
-      <c r="M92" s="3" t="n"/>
-      <c r="O92" s="3" t="n"/>
+      <c r="L92" t="n">
+        <v>91</v>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>2245</t>
+        </is>
+      </c>
+      <c r="O92" s="3" t="n">
+        <v>397.17</v>
+      </c>
       <c r="S92" s="3" t="n"/>
       <c r="T92" s="3" t="n"/>
     </row>
@@ -3392,13 +4848,29 @@
           <t>2300</t>
         </is>
       </c>
-      <c r="D93" s="3" t="n"/>
+      <c r="D93" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E93" s="3" t="n">
         <v>405.2</v>
       </c>
       <c r="I93" s="3" t="n"/>
-      <c r="M93" s="3" t="n"/>
-      <c r="O93" s="3" t="n"/>
+      <c r="L93" t="n">
+        <v>92</v>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="O93" s="3" t="n">
+        <v>397.17</v>
+      </c>
       <c r="S93" s="3" t="n"/>
       <c r="T93" s="3" t="n"/>
     </row>
@@ -3416,13 +4888,29 @@
           <t>2315</t>
         </is>
       </c>
-      <c r="D94" s="3" t="n"/>
+      <c r="D94" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E94" s="3" t="n">
         <v>406.41</v>
       </c>
       <c r="I94" s="3" t="n"/>
-      <c r="M94" s="3" t="n"/>
-      <c r="O94" s="3" t="n"/>
+      <c r="L94" t="n">
+        <v>93</v>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>2315</t>
+        </is>
+      </c>
+      <c r="O94" s="3" t="n">
+        <v>397.17</v>
+      </c>
       <c r="S94" s="3" t="n"/>
       <c r="T94" s="3" t="n"/>
     </row>
@@ -3440,13 +4928,29 @@
           <t>2330</t>
         </is>
       </c>
-      <c r="D95" s="3" t="n"/>
+      <c r="D95" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E95" s="3" t="n">
         <v>397.79</v>
       </c>
       <c r="I95" s="3" t="n"/>
-      <c r="M95" s="3" t="n"/>
-      <c r="O95" s="3" t="n"/>
+      <c r="L95" t="n">
+        <v>94</v>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="O95" s="3" t="n">
+        <v>397.17</v>
+      </c>
       <c r="S95" s="3" t="n"/>
       <c r="T95" s="3" t="n"/>
     </row>
@@ -3464,13 +4968,29 @@
           <t>2345</t>
         </is>
       </c>
-      <c r="D96" s="3" t="n"/>
+      <c r="D96" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E96" s="3" t="n">
         <v>399</v>
       </c>
       <c r="I96" s="3" t="n"/>
-      <c r="M96" s="3" t="n"/>
-      <c r="O96" s="3" t="n"/>
+      <c r="L96" t="n">
+        <v>95</v>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="O96" s="3" t="n">
+        <v>397.17</v>
+      </c>
       <c r="S96" s="3" t="n"/>
       <c r="T96" s="3" t="n"/>
     </row>
@@ -3488,14 +5008,30 @@
           <t>2400</t>
         </is>
       </c>
-      <c r="D97" s="3" t="n"/>
+      <c r="D97" s="3" t="n">
+        <v>343.01</v>
+      </c>
       <c r="E97" s="3" t="n">
         <v>404.42</v>
       </c>
       <c r="H97" s="3" t="n"/>
       <c r="I97" s="3" t="n"/>
-      <c r="M97" s="3" t="n"/>
-      <c r="O97" s="3" t="n"/>
+      <c r="L97" t="n">
+        <v>96</v>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>20260905</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>2400</t>
+        </is>
+      </c>
+      <c r="O97" s="3" t="n">
+        <v>397.17</v>
+      </c>
       <c r="S97" s="3" t="n"/>
       <c r="T97" s="3" t="n"/>
     </row>
@@ -4410,14 +5946,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U2" s="3" t="n"/>
-      <c r="V2" s="3" t="n"/>
-      <c r="W2" s="3" t="n"/>
-      <c r="X2" s="3" t="n"/>
-      <c r="Y2" s="3" t="n"/>
-      <c r="Z2" s="3" t="n"/>
-      <c r="AA2" s="3" t="n"/>
-      <c r="AB2" s="3" t="n"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>00:15</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA2" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB2" s="3" t="n">
+        <v>148</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -4480,14 +6042,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U3" s="3" t="n"/>
-      <c r="V3" s="3" t="n"/>
-      <c r="W3" s="3" t="n"/>
-      <c r="X3" s="3" t="n"/>
-      <c r="Y3" s="3" t="n"/>
-      <c r="Z3" s="3" t="n"/>
-      <c r="AA3" s="3" t="n"/>
-      <c r="AB3" s="3" t="n"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X3" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA3" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB3" s="3" t="n">
+        <v>149</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -4550,14 +6138,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U4" s="3" t="n"/>
-      <c r="V4" s="3" t="n"/>
-      <c r="W4" s="3" t="n"/>
-      <c r="X4" s="3" t="n"/>
-      <c r="Y4" s="3" t="n"/>
-      <c r="Z4" s="3" t="n"/>
-      <c r="AA4" s="3" t="n"/>
-      <c r="AB4" s="3" t="n"/>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>00:45</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA4" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB4" s="3" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4620,14 +6234,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U5" s="3" t="n"/>
-      <c r="V5" s="3" t="n"/>
-      <c r="W5" s="3" t="n"/>
-      <c r="X5" s="3" t="n"/>
-      <c r="Y5" s="3" t="n"/>
-      <c r="Z5" s="3" t="n"/>
-      <c r="AA5" s="3" t="n"/>
-      <c r="AB5" s="3" t="n"/>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA5" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB5" s="3" t="n">
+        <v>144</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4690,14 +6330,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U6" s="3" t="n"/>
-      <c r="V6" s="3" t="n"/>
-      <c r="W6" s="3" t="n"/>
-      <c r="X6" s="3" t="n"/>
-      <c r="Y6" s="3" t="n"/>
-      <c r="Z6" s="3" t="n"/>
-      <c r="AA6" s="3" t="n"/>
-      <c r="AB6" s="3" t="n"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>01:15</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA6" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB6" s="3" t="n">
+        <v>143</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4760,14 +6426,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U7" s="3" t="n"/>
-      <c r="V7" s="3" t="n"/>
-      <c r="W7" s="3" t="n"/>
-      <c r="X7" s="3" t="n"/>
-      <c r="Y7" s="3" t="n"/>
-      <c r="Z7" s="3" t="n"/>
-      <c r="AA7" s="3" t="n"/>
-      <c r="AB7" s="3" t="n"/>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>01:30</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA7" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB7" s="3" t="n">
+        <v>143</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4830,14 +6522,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U8" s="3" t="n"/>
-      <c r="V8" s="3" t="n"/>
-      <c r="W8" s="3" t="n"/>
-      <c r="X8" s="3" t="n"/>
-      <c r="Y8" s="3" t="n"/>
-      <c r="Z8" s="3" t="n"/>
-      <c r="AA8" s="3" t="n"/>
-      <c r="AB8" s="3" t="n"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>01:45</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X8" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA8" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB8" s="3" t="n">
+        <v>146</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4900,14 +6618,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U9" s="3" t="n"/>
-      <c r="V9" s="3" t="n"/>
-      <c r="W9" s="3" t="n"/>
-      <c r="X9" s="3" t="n"/>
-      <c r="Y9" s="3" t="n"/>
-      <c r="Z9" s="3" t="n"/>
-      <c r="AA9" s="3" t="n"/>
-      <c r="AB9" s="3" t="n"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>02:00</t>
+        </is>
+      </c>
+      <c r="U9" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="V9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA9" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB9" s="3" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4970,14 +6714,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U10" s="3" t="n"/>
-      <c r="V10" s="3" t="n"/>
-      <c r="W10" s="3" t="n"/>
-      <c r="X10" s="3" t="n"/>
-      <c r="Y10" s="3" t="n"/>
-      <c r="Z10" s="3" t="n"/>
-      <c r="AA10" s="3" t="n"/>
-      <c r="AB10" s="3" t="n"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>02:15</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="V10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X10" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA10" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB10" s="3" t="n">
+        <v>145</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5040,14 +6810,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U11" s="3" t="n"/>
-      <c r="V11" s="3" t="n"/>
-      <c r="W11" s="3" t="n"/>
-      <c r="X11" s="3" t="n"/>
-      <c r="Y11" s="3" t="n"/>
-      <c r="Z11" s="3" t="n"/>
-      <c r="AA11" s="3" t="n"/>
-      <c r="AB11" s="3" t="n"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>02:30</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="V11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA11" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB11" s="3" t="n">
+        <v>142</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5110,14 +6906,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U12" s="3" t="n"/>
-      <c r="V12" s="3" t="n"/>
-      <c r="W12" s="3" t="n"/>
-      <c r="X12" s="3" t="n"/>
-      <c r="Y12" s="3" t="n"/>
-      <c r="Z12" s="3" t="n"/>
-      <c r="AA12" s="3" t="n"/>
-      <c r="AB12" s="3" t="n"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>02:45</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="V12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X12" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA12" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB12" s="3" t="n">
+        <v>138</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5180,14 +7002,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U13" s="3" t="n"/>
-      <c r="V13" s="3" t="n"/>
-      <c r="W13" s="3" t="n"/>
-      <c r="X13" s="3" t="n"/>
-      <c r="Y13" s="3" t="n"/>
-      <c r="Z13" s="3" t="n"/>
-      <c r="AA13" s="3" t="n"/>
-      <c r="AB13" s="3" t="n"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>03:00</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="V13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X13" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA13" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB13" s="3" t="n">
+        <v>141</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5250,14 +7098,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U14" s="3" t="n"/>
-      <c r="V14" s="3" t="n"/>
-      <c r="W14" s="3" t="n"/>
-      <c r="X14" s="3" t="n"/>
-      <c r="Y14" s="3" t="n"/>
-      <c r="Z14" s="3" t="n"/>
-      <c r="AA14" s="3" t="n"/>
-      <c r="AB14" s="3" t="n"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>03:15</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="V14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X14" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA14" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB14" s="3" t="n">
+        <v>144</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5320,14 +7194,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U15" s="3" t="n"/>
-      <c r="V15" s="3" t="n"/>
-      <c r="W15" s="3" t="n"/>
-      <c r="X15" s="3" t="n"/>
-      <c r="Y15" s="3" t="n"/>
-      <c r="Z15" s="3" t="n"/>
-      <c r="AA15" s="3" t="n"/>
-      <c r="AB15" s="3" t="n"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>03:30</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="V15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA15" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB15" s="3" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5390,14 +7290,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U16" s="3" t="n"/>
-      <c r="V16" s="3" t="n"/>
-      <c r="W16" s="3" t="n"/>
-      <c r="X16" s="3" t="n"/>
-      <c r="Y16" s="3" t="n"/>
-      <c r="Z16" s="3" t="n"/>
-      <c r="AA16" s="3" t="n"/>
-      <c r="AB16" s="3" t="n"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>03:45</t>
+        </is>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="V16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA16" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB16" s="3" t="n">
+        <v>151</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5460,14 +7386,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U17" s="3" t="n"/>
-      <c r="V17" s="3" t="n"/>
-      <c r="W17" s="3" t="n"/>
-      <c r="X17" s="3" t="n"/>
-      <c r="Y17" s="3" t="n"/>
-      <c r="Z17" s="3" t="n"/>
-      <c r="AA17" s="3" t="n"/>
-      <c r="AB17" s="3" t="n"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA17" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB17" s="3" t="n">
+        <v>149</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5530,14 +7482,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U18" s="3" t="n"/>
-      <c r="V18" s="3" t="n"/>
-      <c r="W18" s="3" t="n"/>
-      <c r="X18" s="3" t="n"/>
-      <c r="Y18" s="3" t="n"/>
-      <c r="Z18" s="3" t="n"/>
-      <c r="AA18" s="3" t="n"/>
-      <c r="AB18" s="3" t="n"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="U18" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="V18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W18" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X18" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y18" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA18" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB18" s="3" t="n">
+        <v>146</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5600,14 +7578,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U19" s="3" t="n"/>
-      <c r="V19" s="3" t="n"/>
-      <c r="W19" s="3" t="n"/>
-      <c r="X19" s="3" t="n"/>
-      <c r="Y19" s="3" t="n"/>
-      <c r="Z19" s="3" t="n"/>
-      <c r="AA19" s="3" t="n"/>
-      <c r="AB19" s="3" t="n"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>04:30</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="V19" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W19" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X19" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA19" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB19" s="3" t="n">
+        <v>146</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5670,14 +7674,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U20" s="3" t="n"/>
-      <c r="V20" s="3" t="n"/>
-      <c r="W20" s="3" t="n"/>
-      <c r="X20" s="3" t="n"/>
-      <c r="Y20" s="3" t="n"/>
-      <c r="Z20" s="3" t="n"/>
-      <c r="AA20" s="3" t="n"/>
-      <c r="AB20" s="3" t="n"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>04:45</t>
+        </is>
+      </c>
+      <c r="U20" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="V20" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W20" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X20" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA20" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB20" s="3" t="n">
+        <v>146</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5740,14 +7770,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U21" s="3" t="n"/>
-      <c r="V21" s="3" t="n"/>
-      <c r="W21" s="3" t="n"/>
-      <c r="X21" s="3" t="n"/>
-      <c r="Y21" s="3" t="n"/>
-      <c r="Z21" s="3" t="n"/>
-      <c r="AA21" s="3" t="n"/>
-      <c r="AB21" s="3" t="n"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="V21" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W21" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X21" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z21" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA21" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB21" s="3" t="n">
+        <v>146</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5810,14 +7866,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U22" s="3" t="n"/>
-      <c r="V22" s="3" t="n"/>
-      <c r="W22" s="3" t="n"/>
-      <c r="X22" s="3" t="n"/>
-      <c r="Y22" s="3" t="n"/>
-      <c r="Z22" s="3" t="n"/>
-      <c r="AA22" s="3" t="n"/>
-      <c r="AB22" s="3" t="n"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>05:15</t>
+        </is>
+      </c>
+      <c r="U22" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="V22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W22" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X22" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z22" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA22" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB22" s="3" t="n">
+        <v>146</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5880,14 +7962,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U23" s="3" t="n"/>
-      <c r="V23" s="3" t="n"/>
-      <c r="W23" s="3" t="n"/>
-      <c r="X23" s="3" t="n"/>
-      <c r="Y23" s="3" t="n"/>
-      <c r="Z23" s="3" t="n"/>
-      <c r="AA23" s="3" t="n"/>
-      <c r="AB23" s="3" t="n"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="U23" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="V23" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W23" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X23" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y23" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z23" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA23" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB23" s="3" t="n">
+        <v>144</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5950,14 +8058,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U24" s="3" t="n"/>
-      <c r="V24" s="3" t="n"/>
-      <c r="W24" s="3" t="n"/>
-      <c r="X24" s="3" t="n"/>
-      <c r="Y24" s="3" t="n"/>
-      <c r="Z24" s="3" t="n"/>
-      <c r="AA24" s="3" t="n"/>
-      <c r="AB24" s="3" t="n"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>05:45</t>
+        </is>
+      </c>
+      <c r="U24" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W24" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X24" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y24" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z24" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA24" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB24" s="3" t="n">
+        <v>145</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6020,14 +8154,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U25" s="3" t="n"/>
-      <c r="V25" s="3" t="n"/>
-      <c r="W25" s="3" t="n"/>
-      <c r="X25" s="3" t="n"/>
-      <c r="Y25" s="3" t="n"/>
-      <c r="Z25" s="3" t="n"/>
-      <c r="AA25" s="3" t="n"/>
-      <c r="AB25" s="3" t="n"/>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W25" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X25" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="Y25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z25" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA25" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB25" s="3" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6090,14 +8250,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U26" s="3" t="n"/>
-      <c r="V26" s="3" t="n"/>
-      <c r="W26" s="3" t="n"/>
-      <c r="X26" s="3" t="n"/>
-      <c r="Y26" s="3" t="n"/>
-      <c r="Z26" s="3" t="n"/>
-      <c r="AA26" s="3" t="n"/>
-      <c r="AB26" s="3" t="n"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>06:15</t>
+        </is>
+      </c>
+      <c r="U26" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>224</v>
+      </c>
+      <c r="Y26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA26" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB26" s="3" t="n">
+        <v>143</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6160,14 +8346,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U27" s="3" t="n"/>
-      <c r="V27" s="3" t="n"/>
-      <c r="W27" s="3" t="n"/>
-      <c r="X27" s="3" t="n"/>
-      <c r="Y27" s="3" t="n"/>
-      <c r="Z27" s="3" t="n"/>
-      <c r="AA27" s="3" t="n"/>
-      <c r="AB27" s="3" t="n"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="U27" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="V27" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X27" s="3" t="n">
+        <v>258</v>
+      </c>
+      <c r="Y27" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z27" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA27" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB27" s="3" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -6230,14 +8442,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U28" s="3" t="n"/>
-      <c r="V28" s="3" t="n"/>
-      <c r="W28" s="3" t="n"/>
-      <c r="X28" s="3" t="n"/>
-      <c r="Y28" s="3" t="n"/>
-      <c r="Z28" s="3" t="n"/>
-      <c r="AA28" s="3" t="n"/>
-      <c r="AB28" s="3" t="n"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="U28" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="V28" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X28" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="Y28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z28" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA28" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB28" s="3" t="n">
+        <v>149</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -6300,14 +8538,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U29" s="3" t="n"/>
-      <c r="V29" s="3" t="n"/>
-      <c r="W29" s="3" t="n"/>
-      <c r="X29" s="3" t="n"/>
-      <c r="Y29" s="3" t="n"/>
-      <c r="Z29" s="3" t="n"/>
-      <c r="AA29" s="3" t="n"/>
-      <c r="AB29" s="3" t="n"/>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W29" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X29" s="3" t="n">
+        <v>267</v>
+      </c>
+      <c r="Y29" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z29" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA29" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB29" s="3" t="n">
+        <v>148</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6370,14 +8634,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U30" s="3" t="n"/>
-      <c r="V30" s="3" t="n"/>
-      <c r="W30" s="3" t="n"/>
-      <c r="X30" s="3" t="n"/>
-      <c r="Y30" s="3" t="n"/>
-      <c r="Z30" s="3" t="n"/>
-      <c r="AA30" s="3" t="n"/>
-      <c r="AB30" s="3" t="n"/>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="U30" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="V30" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W30" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X30" s="3" t="n">
+        <v>267</v>
+      </c>
+      <c r="Y30" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z30" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA30" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB30" s="3" t="n">
+        <v>148</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6440,14 +8730,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U31" s="3" t="n"/>
-      <c r="V31" s="3" t="n"/>
-      <c r="W31" s="3" t="n"/>
-      <c r="X31" s="3" t="n"/>
-      <c r="Y31" s="3" t="n"/>
-      <c r="Z31" s="3" t="n"/>
-      <c r="AA31" s="3" t="n"/>
-      <c r="AB31" s="3" t="n"/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="U31" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="V31" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB31" s="3" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6510,14 +8826,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U32" s="3" t="n"/>
-      <c r="V32" s="3" t="n"/>
-      <c r="W32" s="3" t="n"/>
-      <c r="X32" s="3" t="n"/>
-      <c r="Y32" s="3" t="n"/>
-      <c r="Z32" s="3" t="n"/>
-      <c r="AA32" s="3" t="n"/>
-      <c r="AB32" s="3" t="n"/>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="V32" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W32" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X32" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y32" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB32" s="3" t="n">
+        <v>145</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6580,14 +8922,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U33" s="3" t="n"/>
-      <c r="V33" s="3" t="n"/>
-      <c r="W33" s="3" t="n"/>
-      <c r="X33" s="3" t="n"/>
-      <c r="Y33" s="3" t="n"/>
-      <c r="Z33" s="3" t="n"/>
-      <c r="AA33" s="3" t="n"/>
-      <c r="AB33" s="3" t="n"/>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="U33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V33" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W33" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X33" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y33" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB33" s="3" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6650,14 +9018,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U34" s="3" t="n"/>
-      <c r="V34" s="3" t="n"/>
-      <c r="W34" s="3" t="n"/>
-      <c r="X34" s="3" t="n"/>
-      <c r="Y34" s="3" t="n"/>
-      <c r="Z34" s="3" t="n"/>
-      <c r="AA34" s="3" t="n"/>
-      <c r="AB34" s="3" t="n"/>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="U34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W34" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X34" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y34" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB34" s="3" t="n">
+        <v>148</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6720,14 +9114,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U35" s="3" t="n"/>
-      <c r="V35" s="3" t="n"/>
-      <c r="W35" s="3" t="n"/>
-      <c r="X35" s="3" t="n"/>
-      <c r="Y35" s="3" t="n"/>
-      <c r="Z35" s="3" t="n"/>
-      <c r="AA35" s="3" t="n"/>
-      <c r="AB35" s="3" t="n"/>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W35" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X35" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y35" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB35" s="3" t="n">
+        <v>147</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6790,14 +9210,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U36" s="3" t="n"/>
-      <c r="V36" s="3" t="n"/>
-      <c r="W36" s="3" t="n"/>
-      <c r="X36" s="3" t="n"/>
-      <c r="Y36" s="3" t="n"/>
-      <c r="Z36" s="3" t="n"/>
-      <c r="AA36" s="3" t="n"/>
-      <c r="AB36" s="3" t="n"/>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W36" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X36" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y36" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB36" s="3" t="n">
+        <v>148</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6860,14 +9306,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U37" s="3" t="n"/>
-      <c r="V37" s="3" t="n"/>
-      <c r="W37" s="3" t="n"/>
-      <c r="X37" s="3" t="n"/>
-      <c r="Y37" s="3" t="n"/>
-      <c r="Z37" s="3" t="n"/>
-      <c r="AA37" s="3" t="n"/>
-      <c r="AB37" s="3" t="n"/>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="U37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W37" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X37" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y37" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB37" s="3" t="n">
+        <v>146</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6930,14 +9402,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U38" s="3" t="n"/>
-      <c r="V38" s="3" t="n"/>
-      <c r="W38" s="3" t="n"/>
-      <c r="X38" s="3" t="n"/>
-      <c r="Y38" s="3" t="n"/>
-      <c r="Z38" s="3" t="n"/>
-      <c r="AA38" s="3" t="n"/>
-      <c r="AB38" s="3" t="n"/>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="V38" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W38" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X38" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB38" s="3" t="n">
+        <v>144</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -7000,14 +9498,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U39" s="3" t="n"/>
-      <c r="V39" s="3" t="n"/>
-      <c r="W39" s="3" t="n"/>
-      <c r="X39" s="3" t="n"/>
-      <c r="Y39" s="3" t="n"/>
-      <c r="Z39" s="3" t="n"/>
-      <c r="AA39" s="3" t="n"/>
-      <c r="AB39" s="3" t="n"/>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="U39" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="V39" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W39" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X39" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y39" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB39" s="3" t="n">
+        <v>141</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -7070,14 +9594,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U40" s="3" t="n"/>
-      <c r="V40" s="3" t="n"/>
-      <c r="W40" s="3" t="n"/>
-      <c r="X40" s="3" t="n"/>
-      <c r="Y40" s="3" t="n"/>
-      <c r="Z40" s="3" t="n"/>
-      <c r="AA40" s="3" t="n"/>
-      <c r="AB40" s="3" t="n"/>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="U40" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="V40" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W40" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X40" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y40" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB40" s="3" t="n">
+        <v>143</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -7140,14 +9690,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U41" s="3" t="n"/>
-      <c r="V41" s="3" t="n"/>
-      <c r="W41" s="3" t="n"/>
-      <c r="X41" s="3" t="n"/>
-      <c r="Y41" s="3" t="n"/>
-      <c r="Z41" s="3" t="n"/>
-      <c r="AA41" s="3" t="n"/>
-      <c r="AB41" s="3" t="n"/>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="U41" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W41" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X41" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y41" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB41" s="3" t="n">
+        <v>142</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -7210,14 +9786,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U42" s="3" t="n"/>
-      <c r="V42" s="3" t="n"/>
-      <c r="W42" s="3" t="n"/>
-      <c r="X42" s="3" t="n"/>
-      <c r="Y42" s="3" t="n"/>
-      <c r="Z42" s="3" t="n"/>
-      <c r="AA42" s="3" t="n"/>
-      <c r="AB42" s="3" t="n"/>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="V42" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W42" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X42" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y42" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB42" s="3" t="n">
+        <v>143</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -7280,14 +9882,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U43" s="3" t="n"/>
-      <c r="V43" s="3" t="n"/>
-      <c r="W43" s="3" t="n"/>
-      <c r="X43" s="3" t="n"/>
-      <c r="Y43" s="3" t="n"/>
-      <c r="Z43" s="3" t="n"/>
-      <c r="AA43" s="3" t="n"/>
-      <c r="AB43" s="3" t="n"/>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W43" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y43" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB43" s="3" t="n">
+        <v>141</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -7350,14 +9978,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U44" s="3" t="n"/>
-      <c r="V44" s="3" t="n"/>
-      <c r="W44" s="3" t="n"/>
-      <c r="X44" s="3" t="n"/>
-      <c r="Y44" s="3" t="n"/>
-      <c r="Z44" s="3" t="n"/>
-      <c r="AA44" s="3" t="n"/>
-      <c r="AB44" s="3" t="n"/>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="U44" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="V44" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W44" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X44" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y44" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB44" s="3" t="n">
+        <v>141</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -7420,14 +10074,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U45" s="3" t="n"/>
-      <c r="V45" s="3" t="n"/>
-      <c r="W45" s="3" t="n"/>
-      <c r="X45" s="3" t="n"/>
-      <c r="Y45" s="3" t="n"/>
-      <c r="Z45" s="3" t="n"/>
-      <c r="AA45" s="3" t="n"/>
-      <c r="AB45" s="3" t="n"/>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="U45" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="V45" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W45" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X45" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y45" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB45" s="3" t="n">
+        <v>141</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -7490,14 +10170,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U46" s="3" t="n"/>
-      <c r="V46" s="3" t="n"/>
-      <c r="W46" s="3" t="n"/>
-      <c r="X46" s="3" t="n"/>
-      <c r="Y46" s="3" t="n"/>
-      <c r="Z46" s="3" t="n"/>
-      <c r="AA46" s="3" t="n"/>
-      <c r="AB46" s="3" t="n"/>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W46" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y46" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB46" s="3" t="n">
+        <v>145</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -7560,14 +10266,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U47" s="3" t="n"/>
-      <c r="V47" s="3" t="n"/>
-      <c r="W47" s="3" t="n"/>
-      <c r="X47" s="3" t="n"/>
-      <c r="Y47" s="3" t="n"/>
-      <c r="Z47" s="3" t="n"/>
-      <c r="AA47" s="3" t="n"/>
-      <c r="AB47" s="3" t="n"/>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="U47" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="V47" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W47" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X47" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y47" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB47" s="3" t="n">
+        <v>145</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -7630,14 +10362,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U48" s="3" t="n"/>
-      <c r="V48" s="3" t="n"/>
-      <c r="W48" s="3" t="n"/>
-      <c r="X48" s="3" t="n"/>
-      <c r="Y48" s="3" t="n"/>
-      <c r="Z48" s="3" t="n"/>
-      <c r="AA48" s="3" t="n"/>
-      <c r="AB48" s="3" t="n"/>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="U48" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="V48" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W48" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X48" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y48" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB48" s="3" t="n">
+        <v>143</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -7700,14 +10458,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U49" s="3" t="n"/>
-      <c r="V49" s="3" t="n"/>
-      <c r="W49" s="3" t="n"/>
-      <c r="X49" s="3" t="n"/>
-      <c r="Y49" s="3" t="n"/>
-      <c r="Z49" s="3" t="n"/>
-      <c r="AA49" s="3" t="n"/>
-      <c r="AB49" s="3" t="n"/>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="U49" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="V49" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W49" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X49" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y49" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z49" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB49" s="3" t="n">
+        <v>144</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -7770,14 +10554,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U50" s="3" t="n"/>
-      <c r="V50" s="3" t="n"/>
-      <c r="W50" s="3" t="n"/>
-      <c r="X50" s="3" t="n"/>
-      <c r="Y50" s="3" t="n"/>
-      <c r="Z50" s="3" t="n"/>
-      <c r="AA50" s="3" t="n"/>
-      <c r="AB50" s="3" t="n"/>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="U50" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="V50" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W50" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X50" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y50" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB50" s="3" t="n">
+        <v>145</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7840,14 +10650,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U51" s="3" t="n"/>
-      <c r="V51" s="3" t="n"/>
-      <c r="W51" s="3" t="n"/>
-      <c r="X51" s="3" t="n"/>
-      <c r="Y51" s="3" t="n"/>
-      <c r="Z51" s="3" t="n"/>
-      <c r="AA51" s="3" t="n"/>
-      <c r="AB51" s="3" t="n"/>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="U51" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="V51" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W51" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X51" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y51" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB51" s="3" t="n">
+        <v>145</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7910,14 +10746,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U52" s="3" t="n"/>
-      <c r="V52" s="3" t="n"/>
-      <c r="W52" s="3" t="n"/>
-      <c r="X52" s="3" t="n"/>
-      <c r="Y52" s="3" t="n"/>
-      <c r="Z52" s="3" t="n"/>
-      <c r="AA52" s="3" t="n"/>
-      <c r="AB52" s="3" t="n"/>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="U52" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="V52" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W52" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X52" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y52" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB52" s="3" t="n">
+        <v>148</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7980,14 +10842,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U53" s="3" t="n"/>
-      <c r="V53" s="3" t="n"/>
-      <c r="W53" s="3" t="n"/>
-      <c r="X53" s="3" t="n"/>
-      <c r="Y53" s="3" t="n"/>
-      <c r="Z53" s="3" t="n"/>
-      <c r="AA53" s="3" t="n"/>
-      <c r="AB53" s="3" t="n"/>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="U53" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="V53" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W53" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X53" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y53" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB53" s="3" t="n">
+        <v>149</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -8050,14 +10938,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U54" s="3" t="n"/>
-      <c r="V54" s="3" t="n"/>
-      <c r="W54" s="3" t="n"/>
-      <c r="X54" s="3" t="n"/>
-      <c r="Y54" s="3" t="n"/>
-      <c r="Z54" s="3" t="n"/>
-      <c r="AA54" s="3" t="n"/>
-      <c r="AB54" s="3" t="n"/>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="U54" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="V54" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W54" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X54" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y54" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="AB54" s="3" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -8120,14 +11034,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U55" s="3" t="n"/>
-      <c r="V55" s="3" t="n"/>
-      <c r="W55" s="3" t="n"/>
-      <c r="X55" s="3" t="n"/>
-      <c r="Y55" s="3" t="n"/>
-      <c r="Z55" s="3" t="n"/>
-      <c r="AA55" s="3" t="n"/>
-      <c r="AB55" s="3" t="n"/>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="U55" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="V55" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W55" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X55" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y55" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z55" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB55" s="3" t="n">
+        <v>153</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -8190,14 +11130,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U56" s="3" t="n"/>
-      <c r="V56" s="3" t="n"/>
-      <c r="W56" s="3" t="n"/>
-      <c r="X56" s="3" t="n"/>
-      <c r="Y56" s="3" t="n"/>
-      <c r="Z56" s="3" t="n"/>
-      <c r="AA56" s="3" t="n"/>
-      <c r="AB56" s="3" t="n"/>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="U56" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="V56" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W56" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X56" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y56" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA56" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB56" s="3" t="n">
+        <v>154</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -8260,14 +11226,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U57" s="3" t="n"/>
-      <c r="V57" s="3" t="n"/>
-      <c r="W57" s="3" t="n"/>
-      <c r="X57" s="3" t="n"/>
-      <c r="Y57" s="3" t="n"/>
-      <c r="Z57" s="3" t="n"/>
-      <c r="AA57" s="3" t="n"/>
-      <c r="AB57" s="3" t="n"/>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="U57" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="V57" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W57" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X57" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y57" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB57" s="3" t="n">
+        <v>154</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -8330,14 +11322,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U58" s="3" t="n"/>
-      <c r="V58" s="3" t="n"/>
-      <c r="W58" s="3" t="n"/>
-      <c r="X58" s="3" t="n"/>
-      <c r="Y58" s="3" t="n"/>
-      <c r="Z58" s="3" t="n"/>
-      <c r="AA58" s="3" t="n"/>
-      <c r="AB58" s="3" t="n"/>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="U58" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V58" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W58" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X58" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y58" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB58" s="3" t="n">
+        <v>153</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -8400,14 +11418,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U59" s="3" t="n"/>
-      <c r="V59" s="3" t="n"/>
-      <c r="W59" s="3" t="n"/>
-      <c r="X59" s="3" t="n"/>
-      <c r="Y59" s="3" t="n"/>
-      <c r="Z59" s="3" t="n"/>
-      <c r="AA59" s="3" t="n"/>
-      <c r="AB59" s="3" t="n"/>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="U59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V59" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W59" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X59" s="3" t="n">
+        <v>268</v>
+      </c>
+      <c r="Y59" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB59" s="3" t="n">
+        <v>150</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -8470,14 +11514,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U60" s="3" t="n"/>
-      <c r="V60" s="3" t="n"/>
-      <c r="W60" s="3" t="n"/>
-      <c r="X60" s="3" t="n"/>
-      <c r="Y60" s="3" t="n"/>
-      <c r="Z60" s="3" t="n"/>
-      <c r="AA60" s="3" t="n"/>
-      <c r="AB60" s="3" t="n"/>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="U60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W60" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X60" s="3" t="n">
+        <v>267</v>
+      </c>
+      <c r="Y60" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB60" s="3" t="n">
+        <v>151</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -8540,14 +11610,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U61" s="3" t="n"/>
-      <c r="V61" s="3" t="n"/>
-      <c r="W61" s="3" t="n"/>
-      <c r="X61" s="3" t="n"/>
-      <c r="Y61" s="3" t="n"/>
-      <c r="Z61" s="3" t="n"/>
-      <c r="AA61" s="3" t="n"/>
-      <c r="AB61" s="3" t="n"/>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="U61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W61" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X61" s="3" t="n">
+        <v>267</v>
+      </c>
+      <c r="Y61" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB61" s="3" t="n">
+        <v>152</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -8610,14 +11706,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U62" s="3" t="n"/>
-      <c r="V62" s="3" t="n"/>
-      <c r="W62" s="3" t="n"/>
-      <c r="X62" s="3" t="n"/>
-      <c r="Y62" s="3" t="n"/>
-      <c r="Z62" s="3" t="n"/>
-      <c r="AA62" s="3" t="n"/>
-      <c r="AB62" s="3" t="n"/>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="U62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W62" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X62" s="3" t="n">
+        <v>267</v>
+      </c>
+      <c r="Y62" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z62" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB62" s="3" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -8680,14 +11802,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U63" s="3" t="n"/>
-      <c r="V63" s="3" t="n"/>
-      <c r="W63" s="3" t="n"/>
-      <c r="X63" s="3" t="n"/>
-      <c r="Y63" s="3" t="n"/>
-      <c r="Z63" s="3" t="n"/>
-      <c r="AA63" s="3" t="n"/>
-      <c r="AB63" s="3" t="n"/>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="U63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W63" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X63" s="3" t="n">
+        <v>267</v>
+      </c>
+      <c r="Y63" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB63" s="3" t="n">
+        <v>154</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8750,14 +11898,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U64" s="3" t="n"/>
-      <c r="V64" s="3" t="n"/>
-      <c r="W64" s="3" t="n"/>
-      <c r="X64" s="3" t="n"/>
-      <c r="Y64" s="3" t="n"/>
-      <c r="Z64" s="3" t="n"/>
-      <c r="AA64" s="3" t="n"/>
-      <c r="AB64" s="3" t="n"/>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="U64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W64" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X64" s="3" t="n">
+        <v>267</v>
+      </c>
+      <c r="Y64" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB64" s="3" t="n">
+        <v>155</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -8820,14 +11994,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U65" s="3" t="n"/>
-      <c r="V65" s="3" t="n"/>
-      <c r="W65" s="3" t="n"/>
-      <c r="X65" s="3" t="n"/>
-      <c r="Y65" s="3" t="n"/>
-      <c r="Z65" s="3" t="n"/>
-      <c r="AA65" s="3" t="n"/>
-      <c r="AB65" s="3" t="n"/>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="U65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W65" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X65" s="3" t="n">
+        <v>267</v>
+      </c>
+      <c r="Y65" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z65" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA65" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB65" s="3" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -8890,14 +12090,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U66" s="3" t="n"/>
-      <c r="V66" s="3" t="n"/>
-      <c r="W66" s="3" t="n"/>
-      <c r="X66" s="3" t="n"/>
-      <c r="Y66" s="3" t="n"/>
-      <c r="Z66" s="3" t="n"/>
-      <c r="AA66" s="3" t="n"/>
-      <c r="AB66" s="3" t="n"/>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="U66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W66" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X66" s="3" t="n">
+        <v>267</v>
+      </c>
+      <c r="Y66" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA66" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB66" s="3" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -8960,14 +12186,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U67" s="3" t="n"/>
-      <c r="V67" s="3" t="n"/>
-      <c r="W67" s="3" t="n"/>
-      <c r="X67" s="3" t="n"/>
-      <c r="Y67" s="3" t="n"/>
-      <c r="Z67" s="3" t="n"/>
-      <c r="AA67" s="3" t="n"/>
-      <c r="AB67" s="3" t="n"/>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="U67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V67" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W67" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X67" s="3" t="n">
+        <v>267</v>
+      </c>
+      <c r="Y67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA67" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB67" s="3" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -9030,14 +12282,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U68" s="3" t="n"/>
-      <c r="V68" s="3" t="n"/>
-      <c r="W68" s="3" t="n"/>
-      <c r="X68" s="3" t="n"/>
-      <c r="Y68" s="3" t="n"/>
-      <c r="Z68" s="3" t="n"/>
-      <c r="AA68" s="3" t="n"/>
-      <c r="AB68" s="3" t="n"/>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="U68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W68" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X68" s="3" t="n">
+        <v>267</v>
+      </c>
+      <c r="Y68" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA68" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB68" s="3" t="n">
+        <v>157</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -9100,14 +12378,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U69" s="3" t="n"/>
-      <c r="V69" s="3" t="n"/>
-      <c r="W69" s="3" t="n"/>
-      <c r="X69" s="3" t="n"/>
-      <c r="Y69" s="3" t="n"/>
-      <c r="Z69" s="3" t="n"/>
-      <c r="AA69" s="3" t="n"/>
-      <c r="AB69" s="3" t="n"/>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="U69" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="V69" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W69" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X69" s="3" t="n">
+        <v>266</v>
+      </c>
+      <c r="Y69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA69" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="AB69" s="3" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -9170,14 +12474,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U70" s="3" t="n"/>
-      <c r="V70" s="3" t="n"/>
-      <c r="W70" s="3" t="n"/>
-      <c r="X70" s="3" t="n"/>
-      <c r="Y70" s="3" t="n"/>
-      <c r="Z70" s="3" t="n"/>
-      <c r="AA70" s="3" t="n"/>
-      <c r="AB70" s="3" t="n"/>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="U70" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="V70" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W70" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X70" s="3" t="n">
+        <v>267</v>
+      </c>
+      <c r="Y70" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z70" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA70" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB70" s="3" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -9240,14 +12570,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U71" s="3" t="n"/>
-      <c r="V71" s="3" t="n"/>
-      <c r="W71" s="3" t="n"/>
-      <c r="X71" s="3" t="n"/>
-      <c r="Y71" s="3" t="n"/>
-      <c r="Z71" s="3" t="n"/>
-      <c r="AA71" s="3" t="n"/>
-      <c r="AB71" s="3" t="n"/>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="U71" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="V71" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W71" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X71" s="3" t="n">
+        <v>265</v>
+      </c>
+      <c r="Y71" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z71" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA71" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB71" s="3" t="n">
+        <v>157</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -9310,14 +12666,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U72" s="3" t="n"/>
-      <c r="V72" s="3" t="n"/>
-      <c r="W72" s="3" t="n"/>
-      <c r="X72" s="3" t="n"/>
-      <c r="Y72" s="3" t="n"/>
-      <c r="Z72" s="3" t="n"/>
-      <c r="AA72" s="3" t="n"/>
-      <c r="AB72" s="3" t="n"/>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="U72" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="V72" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W72" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X72" s="3" t="n">
+        <v>261</v>
+      </c>
+      <c r="Y72" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z72" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA72" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB72" s="3" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -9380,14 +12762,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U73" s="3" t="n"/>
-      <c r="V73" s="3" t="n"/>
-      <c r="W73" s="3" t="n"/>
-      <c r="X73" s="3" t="n"/>
-      <c r="Y73" s="3" t="n"/>
-      <c r="Z73" s="3" t="n"/>
-      <c r="AA73" s="3" t="n"/>
-      <c r="AB73" s="3" t="n"/>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="U73" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="V73" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W73" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X73" s="3" t="n">
+        <v>246</v>
+      </c>
+      <c r="Y73" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z73" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA73" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB73" s="3" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -9450,14 +12858,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U74" s="3" t="n"/>
-      <c r="V74" s="3" t="n"/>
-      <c r="W74" s="3" t="n"/>
-      <c r="X74" s="3" t="n"/>
-      <c r="Y74" s="3" t="n"/>
-      <c r="Z74" s="3" t="n"/>
-      <c r="AA74" s="3" t="n"/>
-      <c r="AB74" s="3" t="n"/>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="U74" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="V74" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W74" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X74" s="3" t="n">
+        <v>246</v>
+      </c>
+      <c r="Y74" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z74" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA74" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB74" s="3" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -9520,14 +12954,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U75" s="3" t="n"/>
-      <c r="V75" s="3" t="n"/>
-      <c r="W75" s="3" t="n"/>
-      <c r="X75" s="3" t="n"/>
-      <c r="Y75" s="3" t="n"/>
-      <c r="Z75" s="3" t="n"/>
-      <c r="AA75" s="3" t="n"/>
-      <c r="AB75" s="3" t="n"/>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="U75" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="V75" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W75" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X75" s="3" t="n">
+        <v>231</v>
+      </c>
+      <c r="Y75" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z75" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA75" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB75" s="3" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -9590,14 +13050,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U76" s="3" t="n"/>
-      <c r="V76" s="3" t="n"/>
-      <c r="W76" s="3" t="n"/>
-      <c r="X76" s="3" t="n"/>
-      <c r="Y76" s="3" t="n"/>
-      <c r="Z76" s="3" t="n"/>
-      <c r="AA76" s="3" t="n"/>
-      <c r="AB76" s="3" t="n"/>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="U76" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="V76" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W76" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X76" s="3" t="n">
+        <v>115</v>
+      </c>
+      <c r="Y76" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z76" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA76" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB76" s="3" t="n">
+        <v>157</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -9660,14 +13146,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U77" s="3" t="n"/>
-      <c r="V77" s="3" t="n"/>
-      <c r="W77" s="3" t="n"/>
-      <c r="X77" s="3" t="n"/>
-      <c r="Y77" s="3" t="n"/>
-      <c r="Z77" s="3" t="n"/>
-      <c r="AA77" s="3" t="n"/>
-      <c r="AB77" s="3" t="n"/>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="U77" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="V77" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W77" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X77" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y77" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z77" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA77" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB77" s="3" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -9730,14 +13242,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U78" s="3" t="n"/>
-      <c r="V78" s="3" t="n"/>
-      <c r="W78" s="3" t="n"/>
-      <c r="X78" s="3" t="n"/>
-      <c r="Y78" s="3" t="n"/>
-      <c r="Z78" s="3" t="n"/>
-      <c r="AA78" s="3" t="n"/>
-      <c r="AB78" s="3" t="n"/>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="U78" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="V78" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W78" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X78" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y78" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z78" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA78" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB78" s="3" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -9800,14 +13338,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U79" s="3" t="n"/>
-      <c r="V79" s="3" t="n"/>
-      <c r="W79" s="3" t="n"/>
-      <c r="X79" s="3" t="n"/>
-      <c r="Y79" s="3" t="n"/>
-      <c r="Z79" s="3" t="n"/>
-      <c r="AA79" s="3" t="n"/>
-      <c r="AB79" s="3" t="n"/>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="U79" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="V79" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W79" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X79" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y79" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z79" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA79" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB79" s="3" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -9870,14 +13434,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U80" s="3" t="n"/>
-      <c r="V80" s="3" t="n"/>
-      <c r="W80" s="3" t="n"/>
-      <c r="X80" s="3" t="n"/>
-      <c r="Y80" s="3" t="n"/>
-      <c r="Z80" s="3" t="n"/>
-      <c r="AA80" s="3" t="n"/>
-      <c r="AB80" s="3" t="n"/>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="U80" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="V80" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W80" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X80" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y80" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z80" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA80" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB80" s="3" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -9940,14 +13530,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U81" s="3" t="n"/>
-      <c r="V81" s="3" t="n"/>
-      <c r="W81" s="3" t="n"/>
-      <c r="X81" s="3" t="n"/>
-      <c r="Y81" s="3" t="n"/>
-      <c r="Z81" s="3" t="n"/>
-      <c r="AA81" s="3" t="n"/>
-      <c r="AB81" s="3" t="n"/>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="U81" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="V81" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W81" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X81" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y81" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z81" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA81" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB81" s="3" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -10010,14 +13626,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U82" s="3" t="n"/>
-      <c r="V82" s="3" t="n"/>
-      <c r="W82" s="3" t="n"/>
-      <c r="X82" s="3" t="n"/>
-      <c r="Y82" s="3" t="n"/>
-      <c r="Z82" s="3" t="n"/>
-      <c r="AA82" s="3" t="n"/>
-      <c r="AB82" s="3" t="n"/>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="U82" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V82" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W82" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X82" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y82" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z82" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA82" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB82" s="3" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -10080,14 +13722,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U83" s="3" t="n"/>
-      <c r="V83" s="3" t="n"/>
-      <c r="W83" s="3" t="n"/>
-      <c r="X83" s="3" t="n"/>
-      <c r="Y83" s="3" t="n"/>
-      <c r="Z83" s="3" t="n"/>
-      <c r="AA83" s="3" t="n"/>
-      <c r="AB83" s="3" t="n"/>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="U83" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V83" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W83" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X83" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y83" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z83" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA83" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB83" s="3" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -10150,14 +13818,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U84" s="3" t="n"/>
-      <c r="V84" s="3" t="n"/>
-      <c r="W84" s="3" t="n"/>
-      <c r="X84" s="3" t="n"/>
-      <c r="Y84" s="3" t="n"/>
-      <c r="Z84" s="3" t="n"/>
-      <c r="AA84" s="3" t="n"/>
-      <c r="AB84" s="3" t="n"/>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="U84" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V84" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W84" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X84" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y84" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z84" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA84" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB84" s="3" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -10220,14 +13914,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U85" s="3" t="n"/>
-      <c r="V85" s="3" t="n"/>
-      <c r="W85" s="3" t="n"/>
-      <c r="X85" s="3" t="n"/>
-      <c r="Y85" s="3" t="n"/>
-      <c r="Z85" s="3" t="n"/>
-      <c r="AA85" s="3" t="n"/>
-      <c r="AB85" s="3" t="n"/>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="U85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V85" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="W85" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X85" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y85" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z85" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA85" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB85" s="3" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -10290,14 +14010,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U86" s="3" t="n"/>
-      <c r="V86" s="3" t="n"/>
-      <c r="W86" s="3" t="n"/>
-      <c r="X86" s="3" t="n"/>
-      <c r="Y86" s="3" t="n"/>
-      <c r="Z86" s="3" t="n"/>
-      <c r="AA86" s="3" t="n"/>
-      <c r="AB86" s="3" t="n"/>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="U86" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V86" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W86" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X86" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y86" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z86" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA86" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB86" s="3" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -10360,14 +14106,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U87" s="3" t="n"/>
-      <c r="V87" s="3" t="n"/>
-      <c r="W87" s="3" t="n"/>
-      <c r="X87" s="3" t="n"/>
-      <c r="Y87" s="3" t="n"/>
-      <c r="Z87" s="3" t="n"/>
-      <c r="AA87" s="3" t="n"/>
-      <c r="AB87" s="3" t="n"/>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="U87" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V87" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W87" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X87" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y87" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z87" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA87" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB87" s="3" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -10430,14 +14202,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U88" s="3" t="n"/>
-      <c r="V88" s="3" t="n"/>
-      <c r="W88" s="3" t="n"/>
-      <c r="X88" s="3" t="n"/>
-      <c r="Y88" s="3" t="n"/>
-      <c r="Z88" s="3" t="n"/>
-      <c r="AA88" s="3" t="n"/>
-      <c r="AB88" s="3" t="n"/>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="U88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W88" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X88" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y88" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z88" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA88" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB88" s="3" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -10500,14 +14298,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U89" s="3" t="n"/>
-      <c r="V89" s="3" t="n"/>
-      <c r="W89" s="3" t="n"/>
-      <c r="X89" s="3" t="n"/>
-      <c r="Y89" s="3" t="n"/>
-      <c r="Z89" s="3" t="n"/>
-      <c r="AA89" s="3" t="n"/>
-      <c r="AB89" s="3" t="n"/>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="U89" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V89" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W89" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X89" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y89" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z89" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA89" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB89" s="3" t="n">
+        <v>159</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -10570,14 +14394,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U90" s="3" t="n"/>
-      <c r="V90" s="3" t="n"/>
-      <c r="W90" s="3" t="n"/>
-      <c r="X90" s="3" t="n"/>
-      <c r="Y90" s="3" t="n"/>
-      <c r="Z90" s="3" t="n"/>
-      <c r="AA90" s="3" t="n"/>
-      <c r="AB90" s="3" t="n"/>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>22:15</t>
+        </is>
+      </c>
+      <c r="U90" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V90" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W90" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X90" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y90" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z90" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA90" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB90" s="3" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -10640,14 +14490,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U91" s="3" t="n"/>
-      <c r="V91" s="3" t="n"/>
-      <c r="W91" s="3" t="n"/>
-      <c r="X91" s="3" t="n"/>
-      <c r="Y91" s="3" t="n"/>
-      <c r="Z91" s="3" t="n"/>
-      <c r="AA91" s="3" t="n"/>
-      <c r="AB91" s="3" t="n"/>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="U91" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V91" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W91" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X91" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y91" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z91" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA91" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB91" s="3" t="n">
+        <v>160</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -10710,14 +14586,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U92" s="3" t="n"/>
-      <c r="V92" s="3" t="n"/>
-      <c r="W92" s="3" t="n"/>
-      <c r="X92" s="3" t="n"/>
-      <c r="Y92" s="3" t="n"/>
-      <c r="Z92" s="3" t="n"/>
-      <c r="AA92" s="3" t="n"/>
-      <c r="AB92" s="3" t="n"/>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
+      </c>
+      <c r="U92" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V92" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W92" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X92" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y92" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z92" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA92" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB92" s="3" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -10780,14 +14682,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U93" s="3" t="n"/>
-      <c r="V93" s="3" t="n"/>
-      <c r="W93" s="3" t="n"/>
-      <c r="X93" s="3" t="n"/>
-      <c r="Y93" s="3" t="n"/>
-      <c r="Z93" s="3" t="n"/>
-      <c r="AA93" s="3" t="n"/>
-      <c r="AB93" s="3" t="n"/>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="U93" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V93" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W93" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X93" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y93" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z93" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA93" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB93" s="3" t="n">
+        <v>158</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -10850,14 +14778,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U94" s="3" t="n"/>
-      <c r="V94" s="3" t="n"/>
-      <c r="W94" s="3" t="n"/>
-      <c r="X94" s="3" t="n"/>
-      <c r="Y94" s="3" t="n"/>
-      <c r="Z94" s="3" t="n"/>
-      <c r="AA94" s="3" t="n"/>
-      <c r="AB94" s="3" t="n"/>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>23:15</t>
+        </is>
+      </c>
+      <c r="U94" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V94" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W94" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X94" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y94" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z94" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA94" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB94" s="3" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -10920,14 +14874,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U95" s="3" t="n"/>
-      <c r="V95" s="3" t="n"/>
-      <c r="W95" s="3" t="n"/>
-      <c r="X95" s="3" t="n"/>
-      <c r="Y95" s="3" t="n"/>
-      <c r="Z95" s="3" t="n"/>
-      <c r="AA95" s="3" t="n"/>
-      <c r="AB95" s="3" t="n"/>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="U95" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V95" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W95" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X95" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y95" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z95" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA95" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB95" s="3" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -10990,14 +14970,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U96" s="3" t="n"/>
-      <c r="V96" s="3" t="n"/>
-      <c r="W96" s="3" t="n"/>
-      <c r="X96" s="3" t="n"/>
-      <c r="Y96" s="3" t="n"/>
-      <c r="Z96" s="3" t="n"/>
-      <c r="AA96" s="3" t="n"/>
-      <c r="AB96" s="3" t="n"/>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>23:45</t>
+        </is>
+      </c>
+      <c r="U96" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V96" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W96" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X96" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y96" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z96" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA96" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB96" s="3" t="n">
+        <v>156</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -11060,14 +15066,40 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="U97" s="3" t="n"/>
-      <c r="V97" s="3" t="n"/>
-      <c r="W97" s="3" t="n"/>
-      <c r="X97" s="3" t="n"/>
-      <c r="Y97" s="3" t="n"/>
-      <c r="Z97" s="3" t="n"/>
-      <c r="AA97" s="3" t="n"/>
-      <c r="AB97" s="3" t="n"/>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>各时段各类电源的开机台数</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>24:00</t>
+        </is>
+      </c>
+      <c r="U97" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="V97" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W97" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="X97" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y97" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z97" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA97" s="3" t="n">
+        <v>67</v>
+      </c>
+      <c r="AB97" s="3" t="n">
+        <v>157</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13850,7 +17882,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>各时段各类电源的开机台数</t>
+          <t>日前储能充电计划及电价</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -13870,7 +17902,7 @@
         <v>96</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11"/>

--- a/review-results/复盘信息抓取-20260904.xlsx
+++ b/review-results/复盘信息抓取-20260904.xlsx
@@ -5134,8 +5134,27 @@
       <c r="E2" s="3" t="n">
         <v>412.4</v>
       </c>
-      <c r="K2" s="3" t="n"/>
-      <c r="L2" s="3" t="n"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>1158.507</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>372.69</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5159,8 +5178,27 @@
       <c r="E3" s="3" t="n">
         <v>407.413</v>
       </c>
-      <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="n"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>1207.998</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>377.35</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5184,8 +5222,27 @@
       <c r="E4" s="3" t="n">
         <v>403.255</v>
       </c>
-      <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="n"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>1208.924</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>377.35</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5209,8 +5266,27 @@
       <c r="E5" s="3" t="n">
         <v>400.285</v>
       </c>
-      <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="n"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>1198.063</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>376.19</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5234,8 +5310,27 @@
       <c r="E6" s="3" t="n">
         <v>403.348</v>
       </c>
-      <c r="K6" s="3" t="n"/>
-      <c r="L6" s="3" t="n"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>1169.679</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>372.69</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5259,8 +5354,27 @@
       <c r="E7" s="3" t="n">
         <v>410.3</v>
       </c>
-      <c r="K7" s="3" t="n"/>
-      <c r="L7" s="3" t="n"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>1657.153</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>407.63</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5284,8 +5398,27 @@
       <c r="E8" s="3" t="n">
         <v>403.058</v>
       </c>
-      <c r="K8" s="3" t="n"/>
-      <c r="L8" s="3" t="n"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>1179.329</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>372.69</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5309,8 +5442,27 @@
       <c r="E9" s="3" t="n">
         <v>392.29</v>
       </c>
-      <c r="K9" s="3" t="n"/>
-      <c r="L9" s="3" t="n"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>1202.598</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>373.86</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5334,8 +5486,27 @@
       <c r="E10" s="3" t="n">
         <v>364.095</v>
       </c>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>431.512</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>365.38</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5359,8 +5530,27 @@
       <c r="E11" s="3" t="n">
         <v>349.2</v>
       </c>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="n"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>220.998</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>369.07</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5384,8 +5574,27 @@
       <c r="E12" s="3" t="n">
         <v>347.306</v>
       </c>
-      <c r="K12" s="3" t="n"/>
-      <c r="L12" s="3" t="n"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>218.19</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>316.98</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5409,8 +5618,27 @@
       <c r="E13" s="3" t="n">
         <v>373.478</v>
       </c>
-      <c r="K13" s="3" t="n"/>
-      <c r="L13" s="3" t="n"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>110.146</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5434,8 +5662,27 @@
       <c r="E14" s="3" t="n">
         <v>85.753</v>
       </c>
-      <c r="K14" s="3" t="n"/>
-      <c r="L14" s="3" t="n"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>110.77</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5459,8 +5706,27 @@
       <c r="E15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K15" s="3" t="n"/>
-      <c r="L15" s="3" t="n"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>115.465</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5484,8 +5750,27 @@
       <c r="E16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="K16" s="3" t="n"/>
-      <c r="L16" s="3" t="n"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>178.679</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>181</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5509,8 +5794,27 @@
       <c r="E17" s="3" t="n">
         <v>186.35</v>
       </c>
-      <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="n"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>572.275</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>211.55</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5534,8 +5838,27 @@
       <c r="E18" s="3" t="n">
         <v>376.398</v>
       </c>
-      <c r="K18" s="3" t="n"/>
-      <c r="L18" s="3" t="n"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>1131.392</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>402.57</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5559,8 +5882,27 @@
       <c r="E19" s="3" t="n">
         <v>416.558</v>
       </c>
-      <c r="K19" s="3" t="n"/>
-      <c r="L19" s="3" t="n"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>1111.44</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>402.57</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5584,8 +5926,27 @@
       <c r="E20" s="3" t="n">
         <v>417.295</v>
       </c>
-      <c r="K20" s="3" t="n"/>
-      <c r="L20" s="3" t="n"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>1170.627</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>407.63</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5609,8 +5970,27 @@
       <c r="E21" s="3" t="n">
         <v>411.313</v>
       </c>
-      <c r="K21" s="3" t="n"/>
-      <c r="L21" s="3" t="n"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>1088.408</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>399.01</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5634,8 +6014,27 @@
       <c r="E22" s="3" t="n">
         <v>401.93</v>
       </c>
-      <c r="K22" s="3" t="n"/>
-      <c r="L22" s="3" t="n"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>1088.027</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>399.01</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5659,8 +6058,27 @@
       <c r="E23" s="3" t="n">
         <v>397.66</v>
       </c>
-      <c r="K23" s="3" t="n"/>
-      <c r="L23" s="3" t="n"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>1088.079</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>397.17</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5684,8 +6102,27 @@
       <c r="E24" s="3" t="n">
         <v>404.78</v>
       </c>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="3" t="n"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>1088.119</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>397.17</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5709,8 +6146,27 @@
       <c r="E25" s="3" t="n">
         <v>401.905</v>
       </c>
-      <c r="K25" s="3" t="n"/>
-      <c r="L25" s="3" t="n"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>现货日前交易价格曲线</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>1088.613</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>397.17</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15174,9 +15630,7 @@
       <c r="C2" s="3" t="n">
         <v>29688.4</v>
       </c>
-      <c r="D2" s="3" t="n">
-        <v>8424.549999999999</v>
-      </c>
+      <c r="D2" s="3" t="n"/>
       <c r="E2" s="3" t="n">
         <v>0</v>
       </c>
@@ -15201,9 +15655,7 @@
       <c r="C3" s="3" t="n">
         <v>29374.4</v>
       </c>
-      <c r="D3" s="3" t="n">
-        <v>8416.93</v>
-      </c>
+      <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
@@ -15228,9 +15680,7 @@
       <c r="C4" s="3" t="n">
         <v>29136.7</v>
       </c>
-      <c r="D4" s="3" t="n">
-        <v>8408.02</v>
-      </c>
+      <c r="D4" s="3" t="n"/>
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
@@ -15255,9 +15705,7 @@
       <c r="C5" s="3" t="n">
         <v>29083.2</v>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>8397.790000000001</v>
-      </c>
+      <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
@@ -15282,9 +15730,7 @@
       <c r="C6" s="3" t="n">
         <v>28945.2</v>
       </c>
-      <c r="D6" s="3" t="n">
-        <v>8388.360000000001</v>
-      </c>
+      <c r="D6" s="3" t="n"/>
       <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
@@ -15309,9 +15755,7 @@
       <c r="C7" s="3" t="n">
         <v>28797.6</v>
       </c>
-      <c r="D7" s="3" t="n">
-        <v>8382.889999999999</v>
-      </c>
+      <c r="D7" s="3" t="n"/>
       <c r="E7" s="3" t="n">
         <v>0</v>
       </c>
@@ -15336,9 +15780,7 @@
       <c r="C8" s="3" t="n">
         <v>28523.7</v>
       </c>
-      <c r="D8" s="3" t="n">
-        <v>8377.1</v>
-      </c>
+      <c r="D8" s="3" t="n"/>
       <c r="E8" s="3" t="n">
         <v>0</v>
       </c>
@@ -15363,9 +15805,7 @@
       <c r="C9" s="3" t="n">
         <v>28777.8</v>
       </c>
-      <c r="D9" s="3" t="n">
-        <v>8371.959999999999</v>
-      </c>
+      <c r="D9" s="3" t="n"/>
       <c r="E9" s="3" t="n">
         <v>0</v>
       </c>
@@ -15390,9 +15830,7 @@
       <c r="C10" s="3" t="n">
         <v>31474.5</v>
       </c>
-      <c r="D10" s="3" t="n">
-        <v>8363.99</v>
-      </c>
+      <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="n">
         <v>0</v>
       </c>
@@ -15417,9 +15855,7 @@
       <c r="C11" s="3" t="n">
         <v>31312.5</v>
       </c>
-      <c r="D11" s="3" t="n">
-        <v>8356.4</v>
-      </c>
+      <c r="D11" s="3" t="n"/>
       <c r="E11" s="3" t="n">
         <v>0</v>
       </c>
@@ -15444,9 +15880,7 @@
       <c r="C12" s="3" t="n">
         <v>30712.6</v>
       </c>
-      <c r="D12" s="3" t="n">
-        <v>8349.51</v>
-      </c>
+      <c r="D12" s="3" t="n"/>
       <c r="E12" s="3" t="n">
         <v>0</v>
       </c>
@@ -15471,9 +15905,7 @@
       <c r="C13" s="3" t="n">
         <v>29991.9</v>
       </c>
-      <c r="D13" s="3" t="n">
-        <v>8343.209999999999</v>
-      </c>
+      <c r="D13" s="3" t="n"/>
       <c r="E13" s="3" t="n">
         <v>0</v>
       </c>
@@ -15498,9 +15930,7 @@
       <c r="C14" s="3" t="n">
         <v>29579.1</v>
       </c>
-      <c r="D14" s="3" t="n">
-        <v>8339.18</v>
-      </c>
+      <c r="D14" s="3" t="n"/>
       <c r="E14" s="3" t="n">
         <v>0</v>
       </c>
@@ -15525,9 +15955,7 @@
       <c r="C15" s="3" t="n">
         <v>29369</v>
       </c>
-      <c r="D15" s="3" t="n">
-        <v>8334.049999999999</v>
-      </c>
+      <c r="D15" s="3" t="n"/>
       <c r="E15" s="3" t="n">
         <v>0</v>
       </c>
@@ -15552,9 +15980,7 @@
       <c r="C16" s="3" t="n">
         <v>29180.9</v>
       </c>
-      <c r="D16" s="3" t="n">
-        <v>8329.360000000001</v>
-      </c>
+      <c r="D16" s="3" t="n"/>
       <c r="E16" s="3" t="n">
         <v>0</v>
       </c>
@@ -15579,9 +16005,7 @@
       <c r="C17" s="3" t="n">
         <v>28947.5</v>
       </c>
-      <c r="D17" s="3" t="n">
-        <v>8325.75</v>
-      </c>
+      <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="n">
         <v>0</v>
       </c>
@@ -15606,9 +16030,7 @@
       <c r="C18" s="3" t="n">
         <v>28671.8</v>
       </c>
-      <c r="D18" s="3" t="n">
-        <v>8333.85</v>
-      </c>
+      <c r="D18" s="3" t="n"/>
       <c r="E18" s="3" t="n">
         <v>0</v>
       </c>
@@ -15633,9 +16055,7 @@
       <c r="C19" s="3" t="n">
         <v>28547.2</v>
       </c>
-      <c r="D19" s="3" t="n">
-        <v>8331.049999999999</v>
-      </c>
+      <c r="D19" s="3" t="n"/>
       <c r="E19" s="3" t="n">
         <v>0</v>
       </c>
@@ -15660,9 +16080,7 @@
       <c r="C20" s="3" t="n">
         <v>28712.2</v>
       </c>
-      <c r="D20" s="3" t="n">
-        <v>8328.99</v>
-      </c>
+      <c r="D20" s="3" t="n"/>
       <c r="E20" s="3" t="n">
         <v>0</v>
       </c>
@@ -15687,9 +16105,7 @@
       <c r="C21" s="3" t="n">
         <v>28615.2</v>
       </c>
-      <c r="D21" s="3" t="n">
-        <v>8325.870000000001</v>
-      </c>
+      <c r="D21" s="3" t="n"/>
       <c r="E21" s="3" t="n">
         <v>0</v>
       </c>
@@ -15714,9 +16130,7 @@
       <c r="C22" s="3" t="n">
         <v>29216.1</v>
       </c>
-      <c r="D22" s="3" t="n">
-        <v>8328.440000000001</v>
-      </c>
+      <c r="D22" s="3" t="n"/>
       <c r="E22" s="3" t="n">
         <v>0</v>
       </c>
@@ -15741,9 +16155,7 @@
       <c r="C23" s="3" t="n">
         <v>29563</v>
       </c>
-      <c r="D23" s="3" t="n">
-        <v>8333.4</v>
-      </c>
+      <c r="D23" s="3" t="n"/>
       <c r="E23" s="3" t="n">
         <v>0</v>
       </c>
@@ -15768,9 +16180,7 @@
       <c r="C24" s="3" t="n">
         <v>29764</v>
       </c>
-      <c r="D24" s="3" t="n">
-        <v>8340.290000000001</v>
-      </c>
+      <c r="D24" s="3" t="n"/>
       <c r="E24" s="3" t="n">
         <v>0</v>
       </c>
@@ -15795,9 +16205,7 @@
       <c r="C25" s="3" t="n">
         <v>29725.2</v>
       </c>
-      <c r="D25" s="3" t="n">
-        <v>8343.84</v>
-      </c>
+      <c r="D25" s="3" t="n"/>
       <c r="E25" s="3" t="n">
         <v>83.59999999999999</v>
       </c>
@@ -15822,9 +16230,7 @@
       <c r="C26" s="3" t="n">
         <v>30090.2</v>
       </c>
-      <c r="D26" s="3" t="n">
-        <v>8119.43</v>
-      </c>
+      <c r="D26" s="3" t="n"/>
       <c r="E26" s="3" t="n">
         <v>366.8</v>
       </c>
@@ -15849,9 +16255,7 @@
       <c r="C27" s="3" t="n">
         <v>30086.7</v>
       </c>
-      <c r="D27" s="3" t="n">
-        <v>7687.47</v>
-      </c>
+      <c r="D27" s="3" t="n"/>
       <c r="E27" s="3" t="n">
         <v>844.6</v>
       </c>
@@ -15876,9 +16280,7 @@
       <c r="C28" s="3" t="n">
         <v>29857.6</v>
       </c>
-      <c r="D28" s="3" t="n">
-        <v>7004.51</v>
-      </c>
+      <c r="D28" s="3" t="n"/>
       <c r="E28" s="3" t="n">
         <v>1461.4</v>
       </c>
@@ -15903,9 +16305,7 @@
       <c r="C29" s="3" t="n">
         <v>29217.4</v>
       </c>
-      <c r="D29" s="3" t="n">
-        <v>6334.58</v>
-      </c>
+      <c r="D29" s="3" t="n"/>
       <c r="E29" s="3" t="n">
         <v>2130.7</v>
       </c>
@@ -15930,9 +16330,7 @@
       <c r="C30" s="3" t="n">
         <v>28911.7</v>
       </c>
-      <c r="D30" s="3" t="n">
-        <v>5869.85</v>
-      </c>
+      <c r="D30" s="3" t="n"/>
       <c r="E30" s="3" t="n">
         <v>2963.2</v>
       </c>
@@ -15957,9 +16355,7 @@
       <c r="C31" s="3" t="n">
         <v>28534.5</v>
       </c>
-      <c r="D31" s="3" t="n">
-        <v>5390.38</v>
-      </c>
+      <c r="D31" s="3" t="n"/>
       <c r="E31" s="3" t="n">
         <v>3813.4</v>
       </c>
@@ -15984,9 +16380,7 @@
       <c r="C32" s="3" t="n">
         <v>28003.8</v>
       </c>
-      <c r="D32" s="3" t="n">
-        <v>4927.19</v>
-      </c>
+      <c r="D32" s="3" t="n"/>
       <c r="E32" s="3" t="n">
         <v>4416.7</v>
       </c>
@@ -16011,9 +16405,7 @@
       <c r="C33" s="3" t="n">
         <v>27987</v>
       </c>
-      <c r="D33" s="3" t="n">
-        <v>4511.83</v>
-      </c>
+      <c r="D33" s="3" t="n"/>
       <c r="E33" s="3" t="n">
         <v>5337.1</v>
       </c>
@@ -16038,9 +16430,7 @@
       <c r="C34" s="3" t="n">
         <v>28006.9</v>
       </c>
-      <c r="D34" s="3" t="n">
-        <v>4165.79</v>
-      </c>
+      <c r="D34" s="3" t="n"/>
       <c r="E34" s="3" t="n">
         <v>5857.9</v>
       </c>
@@ -16065,9 +16455,7 @@
       <c r="C35" s="3" t="n">
         <v>28293.3</v>
       </c>
-      <c r="D35" s="3" t="n">
-        <v>4113.66</v>
-      </c>
+      <c r="D35" s="3" t="n"/>
       <c r="E35" s="3" t="n">
         <v>6288.4</v>
       </c>
@@ -16092,9 +16480,7 @@
       <c r="C36" s="3" t="n">
         <v>27980.1</v>
       </c>
-      <c r="D36" s="3" t="n">
-        <v>4143.71</v>
-      </c>
+      <c r="D36" s="3" t="n"/>
       <c r="E36" s="3" t="n">
         <v>7031.1</v>
       </c>
@@ -16119,9 +16505,7 @@
       <c r="C37" s="3" t="n">
         <v>27844.2</v>
       </c>
-      <c r="D37" s="3" t="n">
-        <v>4170.04</v>
-      </c>
+      <c r="D37" s="3" t="n"/>
       <c r="E37" s="3" t="n">
         <v>7453.4</v>
       </c>
@@ -16146,9 +16530,7 @@
       <c r="C38" s="3" t="n">
         <v>27717.4</v>
       </c>
-      <c r="D38" s="3" t="n">
-        <v>4194.23</v>
-      </c>
+      <c r="D38" s="3" t="n"/>
       <c r="E38" s="3" t="n">
         <v>7499.2</v>
       </c>
@@ -16173,9 +16555,7 @@
       <c r="C39" s="3" t="n">
         <v>27545.9</v>
       </c>
-      <c r="D39" s="3" t="n">
-        <v>4235.89</v>
-      </c>
+      <c r="D39" s="3" t="n"/>
       <c r="E39" s="3" t="n">
         <v>8375.1</v>
       </c>
@@ -16200,9 +16580,7 @@
       <c r="C40" s="3" t="n">
         <v>27181.5</v>
       </c>
-      <c r="D40" s="3" t="n">
-        <v>4263.49</v>
-      </c>
+      <c r="D40" s="3" t="n"/>
       <c r="E40" s="3" t="n">
         <v>9090.6</v>
       </c>
@@ -16227,9 +16605,7 @@
       <c r="C41" s="3" t="n">
         <v>26877.9</v>
       </c>
-      <c r="D41" s="3" t="n">
-        <v>4284.98</v>
-      </c>
+      <c r="D41" s="3" t="n"/>
       <c r="E41" s="3" t="n">
         <v>9720.700000000001</v>
       </c>
@@ -16254,9 +16630,7 @@
       <c r="C42" s="3" t="n">
         <v>26867.3</v>
       </c>
-      <c r="D42" s="3" t="n">
-        <v>4314.45</v>
-      </c>
+      <c r="D42" s="3" t="n"/>
       <c r="E42" s="3" t="n">
         <v>9961.799999999999</v>
       </c>
@@ -16281,9 +16655,7 @@
       <c r="C43" s="3" t="n">
         <v>26839.7</v>
       </c>
-      <c r="D43" s="3" t="n">
-        <v>4333.82</v>
-      </c>
+      <c r="D43" s="3" t="n"/>
       <c r="E43" s="3" t="n">
         <v>10187.6</v>
       </c>
@@ -16308,9 +16680,7 @@
       <c r="C44" s="3" t="n">
         <v>26940.6</v>
       </c>
-      <c r="D44" s="3" t="n">
-        <v>4353.22</v>
-      </c>
+      <c r="D44" s="3" t="n"/>
       <c r="E44" s="3" t="n">
         <v>10516.6</v>
       </c>
@@ -16335,9 +16705,7 @@
       <c r="C45" s="3" t="n">
         <v>26860.3</v>
       </c>
-      <c r="D45" s="3" t="n">
-        <v>4371.42</v>
-      </c>
+      <c r="D45" s="3" t="n"/>
       <c r="E45" s="3" t="n">
         <v>10653.9</v>
       </c>
@@ -16362,9 +16730,7 @@
       <c r="C46" s="3" t="n">
         <v>28713.6</v>
       </c>
-      <c r="D46" s="3" t="n">
-        <v>4368.44</v>
-      </c>
+      <c r="D46" s="3" t="n"/>
       <c r="E46" s="3" t="n">
         <v>11100.5</v>
       </c>
@@ -16389,9 +16755,7 @@
       <c r="C47" s="3" t="n">
         <v>28442.3</v>
       </c>
-      <c r="D47" s="3" t="n">
-        <v>4392.43</v>
-      </c>
+      <c r="D47" s="3" t="n"/>
       <c r="E47" s="3" t="n">
         <v>11649.5</v>
       </c>
@@ -16416,9 +16780,7 @@
       <c r="C48" s="3" t="n">
         <v>27473</v>
       </c>
-      <c r="D48" s="3" t="n">
-        <v>4391.37</v>
-      </c>
+      <c r="D48" s="3" t="n"/>
       <c r="E48" s="3" t="n">
         <v>11884.1</v>
       </c>
@@ -16443,9 +16805,7 @@
       <c r="C49" s="3" t="n">
         <v>25940.5</v>
       </c>
-      <c r="D49" s="3" t="n">
-        <v>4390.9</v>
-      </c>
+      <c r="D49" s="3" t="n"/>
       <c r="E49" s="3" t="n">
         <v>11858.5</v>
       </c>
@@ -16470,9 +16830,7 @@
       <c r="C50" s="3" t="n">
         <v>25884.6</v>
       </c>
-      <c r="D50" s="3" t="n">
-        <v>4404.88</v>
-      </c>
+      <c r="D50" s="3" t="n"/>
       <c r="E50" s="3" t="n">
         <v>11788</v>
       </c>
@@ -16497,9 +16855,7 @@
       <c r="C51" s="3" t="n">
         <v>25956.6</v>
       </c>
-      <c r="D51" s="3" t="n">
-        <v>4399.19</v>
-      </c>
+      <c r="D51" s="3" t="n"/>
       <c r="E51" s="3" t="n">
         <v>11857</v>
       </c>
@@ -16524,9 +16880,7 @@
       <c r="C52" s="3" t="n">
         <v>25613.1</v>
       </c>
-      <c r="D52" s="3" t="n">
-        <v>4412.46</v>
-      </c>
+      <c r="D52" s="3" t="n"/>
       <c r="E52" s="3" t="n">
         <v>11859.9</v>
       </c>
@@ -16551,9 +16905,7 @@
       <c r="C53" s="3" t="n">
         <v>25437.3</v>
       </c>
-      <c r="D53" s="3" t="n">
-        <v>4407.24</v>
-      </c>
+      <c r="D53" s="3" t="n"/>
       <c r="E53" s="3" t="n">
         <v>11345.5</v>
       </c>
@@ -16578,9 +16930,7 @@
       <c r="C54" s="3" t="n">
         <v>25982.9</v>
       </c>
-      <c r="D54" s="3" t="n">
-        <v>4395.56</v>
-      </c>
+      <c r="D54" s="3" t="n"/>
       <c r="E54" s="3" t="n">
         <v>11545</v>
       </c>
@@ -16605,9 +16955,7 @@
       <c r="C55" s="3" t="n">
         <v>25893.1</v>
       </c>
-      <c r="D55" s="3" t="n">
-        <v>4390.12</v>
-      </c>
+      <c r="D55" s="3" t="n"/>
       <c r="E55" s="3" t="n">
         <v>11689.8</v>
       </c>
@@ -16632,9 +16980,7 @@
       <c r="C56" s="3" t="n">
         <v>26347.5</v>
       </c>
-      <c r="D56" s="3" t="n">
-        <v>4380.01</v>
-      </c>
+      <c r="D56" s="3" t="n"/>
       <c r="E56" s="3" t="n">
         <v>11497.3</v>
       </c>
@@ -16659,9 +17005,7 @@
       <c r="C57" s="3" t="n">
         <v>26461.8</v>
       </c>
-      <c r="D57" s="3" t="n">
-        <v>4371.52</v>
-      </c>
+      <c r="D57" s="3" t="n"/>
       <c r="E57" s="3" t="n">
         <v>11101.1</v>
       </c>
@@ -16686,9 +17030,7 @@
       <c r="C58" s="3" t="n">
         <v>27015.5</v>
       </c>
-      <c r="D58" s="3" t="n">
-        <v>4355.27</v>
-      </c>
+      <c r="D58" s="3" t="n"/>
       <c r="E58" s="3" t="n">
         <v>11139</v>
       </c>
@@ -16713,9 +17055,7 @@
       <c r="C59" s="3" t="n">
         <v>27372.6</v>
       </c>
-      <c r="D59" s="3" t="n">
-        <v>4344.82</v>
-      </c>
+      <c r="D59" s="3" t="n"/>
       <c r="E59" s="3" t="n">
         <v>10668.4</v>
       </c>
@@ -16740,9 +17080,7 @@
       <c r="C60" s="3" t="n">
         <v>27788</v>
       </c>
-      <c r="D60" s="3" t="n">
-        <v>4333.14</v>
-      </c>
+      <c r="D60" s="3" t="n"/>
       <c r="E60" s="3" t="n">
         <v>10211.5</v>
       </c>
@@ -16767,9 +17105,7 @@
       <c r="C61" s="3" t="n">
         <v>28131.9</v>
       </c>
-      <c r="D61" s="3" t="n">
-        <v>4310.95</v>
-      </c>
+      <c r="D61" s="3" t="n"/>
       <c r="E61" s="3" t="n">
         <v>9657.5</v>
       </c>
@@ -16794,9 +17130,7 @@
       <c r="C62" s="3" t="n">
         <v>28341.8</v>
       </c>
-      <c r="D62" s="3" t="n">
-        <v>4420</v>
-      </c>
+      <c r="D62" s="3" t="n"/>
       <c r="E62" s="3" t="n">
         <v>9161.6</v>
       </c>
@@ -16821,9 +17155,7 @@
       <c r="C63" s="3" t="n">
         <v>29270.6</v>
       </c>
-      <c r="D63" s="3" t="n">
-        <v>4837.65</v>
-      </c>
+      <c r="D63" s="3" t="n"/>
       <c r="E63" s="3" t="n">
         <v>8132.5</v>
       </c>
@@ -16848,9 +17180,7 @@
       <c r="C64" s="3" t="n">
         <v>30055.3</v>
       </c>
-      <c r="D64" s="3" t="n">
-        <v>5295.01</v>
-      </c>
+      <c r="D64" s="3" t="n"/>
       <c r="E64" s="3" t="n">
         <v>7500.6</v>
       </c>
@@ -16875,9 +17205,7 @@
       <c r="C65" s="3" t="n">
         <v>30583.7</v>
       </c>
-      <c r="D65" s="3" t="n">
-        <v>6000.27</v>
-      </c>
+      <c r="D65" s="3" t="n"/>
       <c r="E65" s="3" t="n">
         <v>6862.4</v>
       </c>
@@ -16902,9 +17230,7 @@
       <c r="C66" s="3" t="n">
         <v>31672.1</v>
       </c>
-      <c r="D66" s="3" t="n">
-        <v>6700.94</v>
-      </c>
+      <c r="D66" s="3" t="n"/>
       <c r="E66" s="3" t="n">
         <v>5755</v>
       </c>
@@ -16929,9 +17255,7 @@
       <c r="C67" s="3" t="n">
         <v>32459.7</v>
       </c>
-      <c r="D67" s="3" t="n">
-        <v>7202.32</v>
-      </c>
+      <c r="D67" s="3" t="n"/>
       <c r="E67" s="3" t="n">
         <v>5128.9</v>
       </c>
@@ -16956,9 +17280,7 @@
       <c r="C68" s="3" t="n">
         <v>33425.8</v>
       </c>
-      <c r="D68" s="3" t="n">
-        <v>7681.91</v>
-      </c>
+      <c r="D68" s="3" t="n"/>
       <c r="E68" s="3" t="n">
         <v>4427.7</v>
       </c>
@@ -16983,9 +17305,7 @@
       <c r="C69" s="3" t="n">
         <v>34781.3</v>
       </c>
-      <c r="D69" s="3" t="n">
-        <v>8198.389999999999</v>
-      </c>
+      <c r="D69" s="3" t="n"/>
       <c r="E69" s="3" t="n">
         <v>3502.9</v>
       </c>
@@ -17010,9 +17330,7 @@
       <c r="C70" s="3" t="n">
         <v>35930.5</v>
       </c>
-      <c r="D70" s="3" t="n">
-        <v>8662.6</v>
-      </c>
+      <c r="D70" s="3" t="n"/>
       <c r="E70" s="3" t="n">
         <v>2738.2</v>
       </c>
@@ -17037,9 +17355,7 @@
       <c r="C71" s="3" t="n">
         <v>36662.2</v>
       </c>
-      <c r="D71" s="3" t="n">
-        <v>8797.23</v>
-      </c>
+      <c r="D71" s="3" t="n"/>
       <c r="E71" s="3" t="n">
         <v>1989</v>
       </c>
@@ -17064,9 +17380,7 @@
       <c r="C72" s="3" t="n">
         <v>37310.9</v>
       </c>
-      <c r="D72" s="3" t="n">
-        <v>8812.049999999999</v>
-      </c>
+      <c r="D72" s="3" t="n"/>
       <c r="E72" s="3" t="n">
         <v>1306.9</v>
       </c>
@@ -17091,9 +17405,7 @@
       <c r="C73" s="3" t="n">
         <v>37248</v>
       </c>
-      <c r="D73" s="3" t="n">
-        <v>8828.74</v>
-      </c>
+      <c r="D73" s="3" t="n"/>
       <c r="E73" s="3" t="n">
         <v>773.1</v>
       </c>
@@ -17118,9 +17430,7 @@
       <c r="C74" s="3" t="n">
         <v>37578.5</v>
       </c>
-      <c r="D74" s="3" t="n">
-        <v>8857.030000000001</v>
-      </c>
+      <c r="D74" s="3" t="n"/>
       <c r="E74" s="3" t="n">
         <v>425.6</v>
       </c>
@@ -17145,9 +17455,7 @@
       <c r="C75" s="3" t="n">
         <v>37357</v>
       </c>
-      <c r="D75" s="3" t="n">
-        <v>8888.76</v>
-      </c>
+      <c r="D75" s="3" t="n"/>
       <c r="E75" s="3" t="n">
         <v>173.9</v>
       </c>
@@ -17172,9 +17480,7 @@
       <c r="C76" s="3" t="n">
         <v>36822.9</v>
       </c>
-      <c r="D76" s="3" t="n">
-        <v>8877.33</v>
-      </c>
+      <c r="D76" s="3" t="n"/>
       <c r="E76" s="3" t="n">
         <v>8.5</v>
       </c>
@@ -17199,9 +17505,7 @@
       <c r="C77" s="3" t="n">
         <v>37335.2</v>
       </c>
-      <c r="D77" s="3" t="n">
-        <v>8870.4</v>
-      </c>
+      <c r="D77" s="3" t="n"/>
       <c r="E77" s="3" t="n">
         <v>0</v>
       </c>
@@ -17226,9 +17530,7 @@
       <c r="C78" s="3" t="n">
         <v>36841.6</v>
       </c>
-      <c r="D78" s="3" t="n">
-        <v>8866.049999999999</v>
-      </c>
+      <c r="D78" s="3" t="n"/>
       <c r="E78" s="3" t="n">
         <v>0</v>
       </c>
@@ -17253,9 +17555,7 @@
       <c r="C79" s="3" t="n">
         <v>36272.1</v>
       </c>
-      <c r="D79" s="3" t="n">
-        <v>8867.440000000001</v>
-      </c>
+      <c r="D79" s="3" t="n"/>
       <c r="E79" s="3" t="n">
         <v>0</v>
       </c>
@@ -17280,9 +17580,7 @@
       <c r="C80" s="3" t="n">
         <v>36075.1</v>
       </c>
-      <c r="D80" s="3" t="n">
-        <v>8872.02</v>
-      </c>
+      <c r="D80" s="3" t="n"/>
       <c r="E80" s="3" t="n">
         <v>0</v>
       </c>
@@ -17307,9 +17605,7 @@
       <c r="C81" s="3" t="n">
         <v>35606.8</v>
       </c>
-      <c r="D81" s="3" t="n">
-        <v>8878.809999999999</v>
-      </c>
+      <c r="D81" s="3" t="n"/>
       <c r="E81" s="3" t="n">
         <v>0</v>
       </c>
@@ -17334,9 +17630,7 @@
       <c r="C82" s="3" t="n">
         <v>35014.9</v>
       </c>
-      <c r="D82" s="3" t="n">
-        <v>8875.879999999999</v>
-      </c>
+      <c r="D82" s="3" t="n"/>
       <c r="E82" s="3" t="n">
         <v>0</v>
       </c>
@@ -17361,9 +17655,7 @@
       <c r="C83" s="3" t="n">
         <v>34671.3</v>
       </c>
-      <c r="D83" s="3" t="n">
-        <v>8874.76</v>
-      </c>
+      <c r="D83" s="3" t="n"/>
       <c r="E83" s="3" t="n">
         <v>0</v>
       </c>
@@ -17388,9 +17680,7 @@
       <c r="C84" s="3" t="n">
         <v>34660.2</v>
       </c>
-      <c r="D84" s="3" t="n">
-        <v>8876.790000000001</v>
-      </c>
+      <c r="D84" s="3" t="n"/>
       <c r="E84" s="3" t="n">
         <v>0</v>
       </c>
@@ -17415,9 +17705,7 @@
       <c r="C85" s="3" t="n">
         <v>34285.2</v>
       </c>
-      <c r="D85" s="3" t="n">
-        <v>8875.77</v>
-      </c>
+      <c r="D85" s="3" t="n"/>
       <c r="E85" s="3" t="n">
         <v>0</v>
       </c>
@@ -17442,9 +17730,7 @@
       <c r="C86" s="3" t="n">
         <v>33958.5</v>
       </c>
-      <c r="D86" s="3" t="n">
-        <v>8859.9</v>
-      </c>
+      <c r="D86" s="3" t="n"/>
       <c r="E86" s="3" t="n">
         <v>0</v>
       </c>
@@ -17469,9 +17755,7 @@
       <c r="C87" s="3" t="n">
         <v>33657</v>
       </c>
-      <c r="D87" s="3" t="n">
-        <v>8859.27</v>
-      </c>
+      <c r="D87" s="3" t="n"/>
       <c r="E87" s="3" t="n">
         <v>0</v>
       </c>
@@ -17496,9 +17780,7 @@
       <c r="C88" s="3" t="n">
         <v>33385.9</v>
       </c>
-      <c r="D88" s="3" t="n">
-        <v>8856.459999999999</v>
-      </c>
+      <c r="D88" s="3" t="n"/>
       <c r="E88" s="3" t="n">
         <v>0</v>
       </c>
@@ -17523,9 +17805,7 @@
       <c r="C89" s="3" t="n">
         <v>33043.4</v>
       </c>
-      <c r="D89" s="3" t="n">
-        <v>8854.959999999999</v>
-      </c>
+      <c r="D89" s="3" t="n"/>
       <c r="E89" s="3" t="n">
         <v>0</v>
       </c>
@@ -17550,9 +17830,7 @@
       <c r="C90" s="3" t="n">
         <v>32765.2</v>
       </c>
-      <c r="D90" s="3" t="n">
-        <v>8803.33</v>
-      </c>
+      <c r="D90" s="3" t="n"/>
       <c r="E90" s="3" t="n">
         <v>0</v>
       </c>
@@ -17577,9 +17855,7 @@
       <c r="C91" s="3" t="n">
         <v>32586.9</v>
       </c>
-      <c r="D91" s="3" t="n">
-        <v>8803.299999999999</v>
-      </c>
+      <c r="D91" s="3" t="n"/>
       <c r="E91" s="3" t="n">
         <v>0</v>
       </c>
@@ -17604,9 +17880,7 @@
       <c r="C92" s="3" t="n">
         <v>31863.7</v>
       </c>
-      <c r="D92" s="3" t="n">
-        <v>8799.049999999999</v>
-      </c>
+      <c r="D92" s="3" t="n"/>
       <c r="E92" s="3" t="n">
         <v>0</v>
       </c>
@@ -17631,9 +17905,7 @@
       <c r="C93" s="3" t="n">
         <v>31330.7</v>
       </c>
-      <c r="D93" s="3" t="n">
-        <v>8796.74</v>
-      </c>
+      <c r="D93" s="3" t="n"/>
       <c r="E93" s="3" t="n">
         <v>0</v>
       </c>
@@ -17658,9 +17930,7 @@
       <c r="C94" s="3" t="n">
         <v>30595.8</v>
       </c>
-      <c r="D94" s="3" t="n">
-        <v>8797.290000000001</v>
-      </c>
+      <c r="D94" s="3" t="n"/>
       <c r="E94" s="3" t="n">
         <v>0</v>
       </c>
@@ -17685,9 +17955,7 @@
       <c r="C95" s="3" t="n">
         <v>30061.5</v>
       </c>
-      <c r="D95" s="3" t="n">
-        <v>8795.57</v>
-      </c>
+      <c r="D95" s="3" t="n"/>
       <c r="E95" s="3" t="n">
         <v>0</v>
       </c>
@@ -17712,9 +17980,7 @@
       <c r="C96" s="3" t="n">
         <v>29568.1</v>
       </c>
-      <c r="D96" s="3" t="n">
-        <v>8791.440000000001</v>
-      </c>
+      <c r="D96" s="3" t="n"/>
       <c r="E96" s="3" t="n">
         <v>0</v>
       </c>
@@ -17739,9 +18005,7 @@
       <c r="C97" s="3" t="n">
         <v>29535.8</v>
       </c>
-      <c r="D97" s="3" t="n">
-        <v>8791.870000000001</v>
-      </c>
+      <c r="D97" s="3" t="n"/>
       <c r="E97" s="3" t="n">
         <v>0</v>
       </c>
@@ -17804,20 +18068,20 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>实际系统负荷</t>
+          <t>现货日前交易价格曲线</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>新能源实际发电曲线</t>
+          <t>实际系统负荷</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -17830,7 +18094,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>日前非市场化机组总出力</t>
+          <t>新能源实际发电曲线</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -17843,7 +18107,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>省间联络线输电情况</t>
+          <t>发电总出力</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -17856,24 +18120,24 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>各时段各类电源电量</t>
+          <t>省间联络线输电情况</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>960</v>
+        <v>96</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>各时段各类电源的开机台数</t>
+          <t>各时段各类电源电量</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>768</v>
+        <v>960</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
@@ -17882,30 +18146,42 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>日前储能充电计划及电价</t>
+          <t>各时段各类电源的开机台数</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>768</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>实时储能充电计划及电价</t>
+          <t>日前储能充电计划及电价</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>96</v>
       </c>
       <c r="C10" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>实时储能充电计划及电价</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>96</v>
+      </c>
+      <c r="C11" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="11"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/review-results/复盘信息抓取-20260904.xlsx
+++ b/review-results/复盘信息抓取-20260904.xlsx
@@ -15630,7 +15630,9 @@
       <c r="C2" s="3" t="n">
         <v>29688.4</v>
       </c>
-      <c r="D2" s="3" t="n"/>
+      <c r="D2" s="3" t="n">
+        <v>8424.549999999999</v>
+      </c>
       <c r="E2" s="3" t="n">
         <v>0</v>
       </c>
@@ -15655,7 +15657,9 @@
       <c r="C3" s="3" t="n">
         <v>29374.4</v>
       </c>
-      <c r="D3" s="3" t="n"/>
+      <c r="D3" s="3" t="n">
+        <v>8416.93</v>
+      </c>
       <c r="E3" s="3" t="n">
         <v>0</v>
       </c>
@@ -15680,7 +15684,9 @@
       <c r="C4" s="3" t="n">
         <v>29136.7</v>
       </c>
-      <c r="D4" s="3" t="n"/>
+      <c r="D4" s="3" t="n">
+        <v>8408.02</v>
+      </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
@@ -15705,7 +15711,9 @@
       <c r="C5" s="3" t="n">
         <v>29083.2</v>
       </c>
-      <c r="D5" s="3" t="n"/>
+      <c r="D5" s="3" t="n">
+        <v>8397.790000000001</v>
+      </c>
       <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
@@ -15730,7 +15738,9 @@
       <c r="C6" s="3" t="n">
         <v>28945.2</v>
       </c>
-      <c r="D6" s="3" t="n"/>
+      <c r="D6" s="3" t="n">
+        <v>8388.360000000001</v>
+      </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
@@ -15755,7 +15765,9 @@
       <c r="C7" s="3" t="n">
         <v>28797.6</v>
       </c>
-      <c r="D7" s="3" t="n"/>
+      <c r="D7" s="3" t="n">
+        <v>8382.889999999999</v>
+      </c>
       <c r="E7" s="3" t="n">
         <v>0</v>
       </c>
@@ -15780,7 +15792,9 @@
       <c r="C8" s="3" t="n">
         <v>28523.7</v>
       </c>
-      <c r="D8" s="3" t="n"/>
+      <c r="D8" s="3" t="n">
+        <v>8377.1</v>
+      </c>
       <c r="E8" s="3" t="n">
         <v>0</v>
       </c>
@@ -15805,7 +15819,9 @@
       <c r="C9" s="3" t="n">
         <v>28777.8</v>
       </c>
-      <c r="D9" s="3" t="n"/>
+      <c r="D9" s="3" t="n">
+        <v>8371.959999999999</v>
+      </c>
       <c r="E9" s="3" t="n">
         <v>0</v>
       </c>
@@ -15830,7 +15846,9 @@
       <c r="C10" s="3" t="n">
         <v>31474.5</v>
       </c>
-      <c r="D10" s="3" t="n"/>
+      <c r="D10" s="3" t="n">
+        <v>8363.99</v>
+      </c>
       <c r="E10" s="3" t="n">
         <v>0</v>
       </c>
@@ -15855,7 +15873,9 @@
       <c r="C11" s="3" t="n">
         <v>31312.5</v>
       </c>
-      <c r="D11" s="3" t="n"/>
+      <c r="D11" s="3" t="n">
+        <v>8356.4</v>
+      </c>
       <c r="E11" s="3" t="n">
         <v>0</v>
       </c>
@@ -15880,7 +15900,9 @@
       <c r="C12" s="3" t="n">
         <v>30712.6</v>
       </c>
-      <c r="D12" s="3" t="n"/>
+      <c r="D12" s="3" t="n">
+        <v>8349.51</v>
+      </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
       </c>
@@ -15905,7 +15927,9 @@
       <c r="C13" s="3" t="n">
         <v>29991.9</v>
       </c>
-      <c r="D13" s="3" t="n"/>
+      <c r="D13" s="3" t="n">
+        <v>8343.209999999999</v>
+      </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
       </c>
@@ -15930,7 +15954,9 @@
       <c r="C14" s="3" t="n">
         <v>29579.1</v>
       </c>
-      <c r="D14" s="3" t="n"/>
+      <c r="D14" s="3" t="n">
+        <v>8339.18</v>
+      </c>
       <c r="E14" s="3" t="n">
         <v>0</v>
       </c>
@@ -15955,7 +15981,9 @@
       <c r="C15" s="3" t="n">
         <v>29369</v>
       </c>
-      <c r="D15" s="3" t="n"/>
+      <c r="D15" s="3" t="n">
+        <v>8334.049999999999</v>
+      </c>
       <c r="E15" s="3" t="n">
         <v>0</v>
       </c>
@@ -15980,7 +16008,9 @@
       <c r="C16" s="3" t="n">
         <v>29180.9</v>
       </c>
-      <c r="D16" s="3" t="n"/>
+      <c r="D16" s="3" t="n">
+        <v>8329.360000000001</v>
+      </c>
       <c r="E16" s="3" t="n">
         <v>0</v>
       </c>
@@ -16005,7 +16035,9 @@
       <c r="C17" s="3" t="n">
         <v>28947.5</v>
       </c>
-      <c r="D17" s="3" t="n"/>
+      <c r="D17" s="3" t="n">
+        <v>8325.75</v>
+      </c>
       <c r="E17" s="3" t="n">
         <v>0</v>
       </c>
@@ -16030,7 +16062,9 @@
       <c r="C18" s="3" t="n">
         <v>28671.8</v>
       </c>
-      <c r="D18" s="3" t="n"/>
+      <c r="D18" s="3" t="n">
+        <v>8333.85</v>
+      </c>
       <c r="E18" s="3" t="n">
         <v>0</v>
       </c>
@@ -16055,7 +16089,9 @@
       <c r="C19" s="3" t="n">
         <v>28547.2</v>
       </c>
-      <c r="D19" s="3" t="n"/>
+      <c r="D19" s="3" t="n">
+        <v>8331.049999999999</v>
+      </c>
       <c r="E19" s="3" t="n">
         <v>0</v>
       </c>
@@ -16080,7 +16116,9 @@
       <c r="C20" s="3" t="n">
         <v>28712.2</v>
       </c>
-      <c r="D20" s="3" t="n"/>
+      <c r="D20" s="3" t="n">
+        <v>8328.99</v>
+      </c>
       <c r="E20" s="3" t="n">
         <v>0</v>
       </c>
@@ -16105,7 +16143,9 @@
       <c r="C21" s="3" t="n">
         <v>28615.2</v>
       </c>
-      <c r="D21" s="3" t="n"/>
+      <c r="D21" s="3" t="n">
+        <v>8325.870000000001</v>
+      </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
       </c>
@@ -16130,7 +16170,9 @@
       <c r="C22" s="3" t="n">
         <v>29216.1</v>
       </c>
-      <c r="D22" s="3" t="n"/>
+      <c r="D22" s="3" t="n">
+        <v>8328.440000000001</v>
+      </c>
       <c r="E22" s="3" t="n">
         <v>0</v>
       </c>
@@ -16155,7 +16197,9 @@
       <c r="C23" s="3" t="n">
         <v>29563</v>
       </c>
-      <c r="D23" s="3" t="n"/>
+      <c r="D23" s="3" t="n">
+        <v>8333.4</v>
+      </c>
       <c r="E23" s="3" t="n">
         <v>0</v>
       </c>
@@ -16180,7 +16224,9 @@
       <c r="C24" s="3" t="n">
         <v>29764</v>
       </c>
-      <c r="D24" s="3" t="n"/>
+      <c r="D24" s="3" t="n">
+        <v>8340.290000000001</v>
+      </c>
       <c r="E24" s="3" t="n">
         <v>0</v>
       </c>
@@ -16205,7 +16251,9 @@
       <c r="C25" s="3" t="n">
         <v>29725.2</v>
       </c>
-      <c r="D25" s="3" t="n"/>
+      <c r="D25" s="3" t="n">
+        <v>8343.84</v>
+      </c>
       <c r="E25" s="3" t="n">
         <v>83.59999999999999</v>
       </c>
@@ -16230,7 +16278,9 @@
       <c r="C26" s="3" t="n">
         <v>30090.2</v>
       </c>
-      <c r="D26" s="3" t="n"/>
+      <c r="D26" s="3" t="n">
+        <v>8119.43</v>
+      </c>
       <c r="E26" s="3" t="n">
         <v>366.8</v>
       </c>
@@ -16255,7 +16305,9 @@
       <c r="C27" s="3" t="n">
         <v>30086.7</v>
       </c>
-      <c r="D27" s="3" t="n"/>
+      <c r="D27" s="3" t="n">
+        <v>7687.47</v>
+      </c>
       <c r="E27" s="3" t="n">
         <v>844.6</v>
       </c>
@@ -16280,7 +16332,9 @@
       <c r="C28" s="3" t="n">
         <v>29857.6</v>
       </c>
-      <c r="D28" s="3" t="n"/>
+      <c r="D28" s="3" t="n">
+        <v>7004.51</v>
+      </c>
       <c r="E28" s="3" t="n">
         <v>1461.4</v>
       </c>
@@ -16305,7 +16359,9 @@
       <c r="C29" s="3" t="n">
         <v>29217.4</v>
       </c>
-      <c r="D29" s="3" t="n"/>
+      <c r="D29" s="3" t="n">
+        <v>6334.58</v>
+      </c>
       <c r="E29" s="3" t="n">
         <v>2130.7</v>
       </c>
@@ -16330,7 +16386,9 @@
       <c r="C30" s="3" t="n">
         <v>28911.7</v>
       </c>
-      <c r="D30" s="3" t="n"/>
+      <c r="D30" s="3" t="n">
+        <v>5869.85</v>
+      </c>
       <c r="E30" s="3" t="n">
         <v>2963.2</v>
       </c>
@@ -16355,7 +16413,9 @@
       <c r="C31" s="3" t="n">
         <v>28534.5</v>
       </c>
-      <c r="D31" s="3" t="n"/>
+      <c r="D31" s="3" t="n">
+        <v>5390.38</v>
+      </c>
       <c r="E31" s="3" t="n">
         <v>3813.4</v>
       </c>
@@ -16380,7 +16440,9 @@
       <c r="C32" s="3" t="n">
         <v>28003.8</v>
       </c>
-      <c r="D32" s="3" t="n"/>
+      <c r="D32" s="3" t="n">
+        <v>4927.19</v>
+      </c>
       <c r="E32" s="3" t="n">
         <v>4416.7</v>
       </c>
@@ -16405,7 +16467,9 @@
       <c r="C33" s="3" t="n">
         <v>27987</v>
       </c>
-      <c r="D33" s="3" t="n"/>
+      <c r="D33" s="3" t="n">
+        <v>4511.83</v>
+      </c>
       <c r="E33" s="3" t="n">
         <v>5337.1</v>
       </c>
@@ -16430,7 +16494,9 @@
       <c r="C34" s="3" t="n">
         <v>28006.9</v>
       </c>
-      <c r="D34" s="3" t="n"/>
+      <c r="D34" s="3" t="n">
+        <v>4165.79</v>
+      </c>
       <c r="E34" s="3" t="n">
         <v>5857.9</v>
       </c>
@@ -16455,7 +16521,9 @@
       <c r="C35" s="3" t="n">
         <v>28293.3</v>
       </c>
-      <c r="D35" s="3" t="n"/>
+      <c r="D35" s="3" t="n">
+        <v>4113.66</v>
+      </c>
       <c r="E35" s="3" t="n">
         <v>6288.4</v>
       </c>
@@ -16480,7 +16548,9 @@
       <c r="C36" s="3" t="n">
         <v>27980.1</v>
       </c>
-      <c r="D36" s="3" t="n"/>
+      <c r="D36" s="3" t="n">
+        <v>4143.71</v>
+      </c>
       <c r="E36" s="3" t="n">
         <v>7031.1</v>
       </c>
@@ -16505,7 +16575,9 @@
       <c r="C37" s="3" t="n">
         <v>27844.2</v>
       </c>
-      <c r="D37" s="3" t="n"/>
+      <c r="D37" s="3" t="n">
+        <v>4170.04</v>
+      </c>
       <c r="E37" s="3" t="n">
         <v>7453.4</v>
       </c>
@@ -16530,7 +16602,9 @@
       <c r="C38" s="3" t="n">
         <v>27717.4</v>
       </c>
-      <c r="D38" s="3" t="n"/>
+      <c r="D38" s="3" t="n">
+        <v>4194.23</v>
+      </c>
       <c r="E38" s="3" t="n">
         <v>7499.2</v>
       </c>
@@ -16555,7 +16629,9 @@
       <c r="C39" s="3" t="n">
         <v>27545.9</v>
       </c>
-      <c r="D39" s="3" t="n"/>
+      <c r="D39" s="3" t="n">
+        <v>4235.89</v>
+      </c>
       <c r="E39" s="3" t="n">
         <v>8375.1</v>
       </c>
@@ -16580,7 +16656,9 @@
       <c r="C40" s="3" t="n">
         <v>27181.5</v>
       </c>
-      <c r="D40" s="3" t="n"/>
+      <c r="D40" s="3" t="n">
+        <v>4263.49</v>
+      </c>
       <c r="E40" s="3" t="n">
         <v>9090.6</v>
       </c>
@@ -16605,7 +16683,9 @@
       <c r="C41" s="3" t="n">
         <v>26877.9</v>
       </c>
-      <c r="D41" s="3" t="n"/>
+      <c r="D41" s="3" t="n">
+        <v>4284.98</v>
+      </c>
       <c r="E41" s="3" t="n">
         <v>9720.700000000001</v>
       </c>
@@ -16630,7 +16710,9 @@
       <c r="C42" s="3" t="n">
         <v>26867.3</v>
       </c>
-      <c r="D42" s="3" t="n"/>
+      <c r="D42" s="3" t="n">
+        <v>4314.45</v>
+      </c>
       <c r="E42" s="3" t="n">
         <v>9961.799999999999</v>
       </c>
@@ -16655,7 +16737,9 @@
       <c r="C43" s="3" t="n">
         <v>26839.7</v>
       </c>
-      <c r="D43" s="3" t="n"/>
+      <c r="D43" s="3" t="n">
+        <v>4333.82</v>
+      </c>
       <c r="E43" s="3" t="n">
         <v>10187.6</v>
       </c>
@@ -16680,7 +16764,9 @@
       <c r="C44" s="3" t="n">
         <v>26940.6</v>
       </c>
-      <c r="D44" s="3" t="n"/>
+      <c r="D44" s="3" t="n">
+        <v>4353.22</v>
+      </c>
       <c r="E44" s="3" t="n">
         <v>10516.6</v>
       </c>
@@ -16705,7 +16791,9 @@
       <c r="C45" s="3" t="n">
         <v>26860.3</v>
       </c>
-      <c r="D45" s="3" t="n"/>
+      <c r="D45" s="3" t="n">
+        <v>4371.42</v>
+      </c>
       <c r="E45" s="3" t="n">
         <v>10653.9</v>
       </c>
@@ -16730,7 +16818,9 @@
       <c r="C46" s="3" t="n">
         <v>28713.6</v>
       </c>
-      <c r="D46" s="3" t="n"/>
+      <c r="D46" s="3" t="n">
+        <v>4368.44</v>
+      </c>
       <c r="E46" s="3" t="n">
         <v>11100.5</v>
       </c>
@@ -16755,7 +16845,9 @@
       <c r="C47" s="3" t="n">
         <v>28442.3</v>
       </c>
-      <c r="D47" s="3" t="n"/>
+      <c r="D47" s="3" t="n">
+        <v>4392.43</v>
+      </c>
       <c r="E47" s="3" t="n">
         <v>11649.5</v>
       </c>
@@ -16780,7 +16872,9 @@
       <c r="C48" s="3" t="n">
         <v>27473</v>
       </c>
-      <c r="D48" s="3" t="n"/>
+      <c r="D48" s="3" t="n">
+        <v>4391.37</v>
+      </c>
       <c r="E48" s="3" t="n">
         <v>11884.1</v>
       </c>
@@ -16805,7 +16899,9 @@
       <c r="C49" s="3" t="n">
         <v>25940.5</v>
       </c>
-      <c r="D49" s="3" t="n"/>
+      <c r="D49" s="3" t="n">
+        <v>4390.9</v>
+      </c>
       <c r="E49" s="3" t="n">
         <v>11858.5</v>
       </c>
@@ -16830,7 +16926,9 @@
       <c r="C50" s="3" t="n">
         <v>25884.6</v>
       </c>
-      <c r="D50" s="3" t="n"/>
+      <c r="D50" s="3" t="n">
+        <v>4404.88</v>
+      </c>
       <c r="E50" s="3" t="n">
         <v>11788</v>
       </c>
@@ -16855,7 +16953,9 @@
       <c r="C51" s="3" t="n">
         <v>25956.6</v>
       </c>
-      <c r="D51" s="3" t="n"/>
+      <c r="D51" s="3" t="n">
+        <v>4399.19</v>
+      </c>
       <c r="E51" s="3" t="n">
         <v>11857</v>
       </c>
@@ -16880,7 +16980,9 @@
       <c r="C52" s="3" t="n">
         <v>25613.1</v>
       </c>
-      <c r="D52" s="3" t="n"/>
+      <c r="D52" s="3" t="n">
+        <v>4412.46</v>
+      </c>
       <c r="E52" s="3" t="n">
         <v>11859.9</v>
       </c>
@@ -16905,7 +17007,9 @@
       <c r="C53" s="3" t="n">
         <v>25437.3</v>
       </c>
-      <c r="D53" s="3" t="n"/>
+      <c r="D53" s="3" t="n">
+        <v>4407.24</v>
+      </c>
       <c r="E53" s="3" t="n">
         <v>11345.5</v>
       </c>
@@ -16930,7 +17034,9 @@
       <c r="C54" s="3" t="n">
         <v>25982.9</v>
       </c>
-      <c r="D54" s="3" t="n"/>
+      <c r="D54" s="3" t="n">
+        <v>4395.56</v>
+      </c>
       <c r="E54" s="3" t="n">
         <v>11545</v>
       </c>
@@ -16955,7 +17061,9 @@
       <c r="C55" s="3" t="n">
         <v>25893.1</v>
       </c>
-      <c r="D55" s="3" t="n"/>
+      <c r="D55" s="3" t="n">
+        <v>4390.12</v>
+      </c>
       <c r="E55" s="3" t="n">
         <v>11689.8</v>
       </c>
@@ -16980,7 +17088,9 @@
       <c r="C56" s="3" t="n">
         <v>26347.5</v>
       </c>
-      <c r="D56" s="3" t="n"/>
+      <c r="D56" s="3" t="n">
+        <v>4380.01</v>
+      </c>
       <c r="E56" s="3" t="n">
         <v>11497.3</v>
       </c>
@@ -17005,7 +17115,9 @@
       <c r="C57" s="3" t="n">
         <v>26461.8</v>
       </c>
-      <c r="D57" s="3" t="n"/>
+      <c r="D57" s="3" t="n">
+        <v>4371.52</v>
+      </c>
       <c r="E57" s="3" t="n">
         <v>11101.1</v>
       </c>
@@ -17030,7 +17142,9 @@
       <c r="C58" s="3" t="n">
         <v>27015.5</v>
       </c>
-      <c r="D58" s="3" t="n"/>
+      <c r="D58" s="3" t="n">
+        <v>4355.27</v>
+      </c>
       <c r="E58" s="3" t="n">
         <v>11139</v>
       </c>
@@ -17055,7 +17169,9 @@
       <c r="C59" s="3" t="n">
         <v>27372.6</v>
       </c>
-      <c r="D59" s="3" t="n"/>
+      <c r="D59" s="3" t="n">
+        <v>4344.82</v>
+      </c>
       <c r="E59" s="3" t="n">
         <v>10668.4</v>
       </c>
@@ -17080,7 +17196,9 @@
       <c r="C60" s="3" t="n">
         <v>27788</v>
       </c>
-      <c r="D60" s="3" t="n"/>
+      <c r="D60" s="3" t="n">
+        <v>4333.14</v>
+      </c>
       <c r="E60" s="3" t="n">
         <v>10211.5</v>
       </c>
@@ -17105,7 +17223,9 @@
       <c r="C61" s="3" t="n">
         <v>28131.9</v>
       </c>
-      <c r="D61" s="3" t="n"/>
+      <c r="D61" s="3" t="n">
+        <v>4310.95</v>
+      </c>
       <c r="E61" s="3" t="n">
         <v>9657.5</v>
       </c>
@@ -17130,7 +17250,9 @@
       <c r="C62" s="3" t="n">
         <v>28341.8</v>
       </c>
-      <c r="D62" s="3" t="n"/>
+      <c r="D62" s="3" t="n">
+        <v>4420</v>
+      </c>
       <c r="E62" s="3" t="n">
         <v>9161.6</v>
       </c>
@@ -17155,7 +17277,9 @@
       <c r="C63" s="3" t="n">
         <v>29270.6</v>
       </c>
-      <c r="D63" s="3" t="n"/>
+      <c r="D63" s="3" t="n">
+        <v>4837.65</v>
+      </c>
       <c r="E63" s="3" t="n">
         <v>8132.5</v>
       </c>
@@ -17180,7 +17304,9 @@
       <c r="C64" s="3" t="n">
         <v>30055.3</v>
       </c>
-      <c r="D64" s="3" t="n"/>
+      <c r="D64" s="3" t="n">
+        <v>5295.01</v>
+      </c>
       <c r="E64" s="3" t="n">
         <v>7500.6</v>
       </c>
@@ -17205,7 +17331,9 @@
       <c r="C65" s="3" t="n">
         <v>30583.7</v>
       </c>
-      <c r="D65" s="3" t="n"/>
+      <c r="D65" s="3" t="n">
+        <v>6000.27</v>
+      </c>
       <c r="E65" s="3" t="n">
         <v>6862.4</v>
       </c>
@@ -17230,7 +17358,9 @@
       <c r="C66" s="3" t="n">
         <v>31672.1</v>
       </c>
-      <c r="D66" s="3" t="n"/>
+      <c r="D66" s="3" t="n">
+        <v>6700.94</v>
+      </c>
       <c r="E66" s="3" t="n">
         <v>5755</v>
       </c>
@@ -17255,7 +17385,9 @@
       <c r="C67" s="3" t="n">
         <v>32459.7</v>
       </c>
-      <c r="D67" s="3" t="n"/>
+      <c r="D67" s="3" t="n">
+        <v>7202.32</v>
+      </c>
       <c r="E67" s="3" t="n">
         <v>5128.9</v>
       </c>
@@ -17280,7 +17412,9 @@
       <c r="C68" s="3" t="n">
         <v>33425.8</v>
       </c>
-      <c r="D68" s="3" t="n"/>
+      <c r="D68" s="3" t="n">
+        <v>7681.91</v>
+      </c>
       <c r="E68" s="3" t="n">
         <v>4427.7</v>
       </c>
@@ -17305,7 +17439,9 @@
       <c r="C69" s="3" t="n">
         <v>34781.3</v>
       </c>
-      <c r="D69" s="3" t="n"/>
+      <c r="D69" s="3" t="n">
+        <v>8198.389999999999</v>
+      </c>
       <c r="E69" s="3" t="n">
         <v>3502.9</v>
       </c>
@@ -17330,7 +17466,9 @@
       <c r="C70" s="3" t="n">
         <v>35930.5</v>
       </c>
-      <c r="D70" s="3" t="n"/>
+      <c r="D70" s="3" t="n">
+        <v>8662.6</v>
+      </c>
       <c r="E70" s="3" t="n">
         <v>2738.2</v>
       </c>
@@ -17355,7 +17493,9 @@
       <c r="C71" s="3" t="n">
         <v>36662.2</v>
       </c>
-      <c r="D71" s="3" t="n"/>
+      <c r="D71" s="3" t="n">
+        <v>8797.23</v>
+      </c>
       <c r="E71" s="3" t="n">
         <v>1989</v>
       </c>
@@ -17380,7 +17520,9 @@
       <c r="C72" s="3" t="n">
         <v>37310.9</v>
       </c>
-      <c r="D72" s="3" t="n"/>
+      <c r="D72" s="3" t="n">
+        <v>8812.049999999999</v>
+      </c>
       <c r="E72" s="3" t="n">
         <v>1306.9</v>
       </c>
@@ -17405,7 +17547,9 @@
       <c r="C73" s="3" t="n">
         <v>37248</v>
       </c>
-      <c r="D73" s="3" t="n"/>
+      <c r="D73" s="3" t="n">
+        <v>8828.74</v>
+      </c>
       <c r="E73" s="3" t="n">
         <v>773.1</v>
       </c>
@@ -17430,7 +17574,9 @@
       <c r="C74" s="3" t="n">
         <v>37578.5</v>
       </c>
-      <c r="D74" s="3" t="n"/>
+      <c r="D74" s="3" t="n">
+        <v>8857.030000000001</v>
+      </c>
       <c r="E74" s="3" t="n">
         <v>425.6</v>
       </c>
@@ -17455,7 +17601,9 @@
       <c r="C75" s="3" t="n">
         <v>37357</v>
       </c>
-      <c r="D75" s="3" t="n"/>
+      <c r="D75" s="3" t="n">
+        <v>8888.76</v>
+      </c>
       <c r="E75" s="3" t="n">
         <v>173.9</v>
       </c>
@@ -17480,7 +17628,9 @@
       <c r="C76" s="3" t="n">
         <v>36822.9</v>
       </c>
-      <c r="D76" s="3" t="n"/>
+      <c r="D76" s="3" t="n">
+        <v>8877.33</v>
+      </c>
       <c r="E76" s="3" t="n">
         <v>8.5</v>
       </c>
@@ -17505,7 +17655,9 @@
       <c r="C77" s="3" t="n">
         <v>37335.2</v>
       </c>
-      <c r="D77" s="3" t="n"/>
+      <c r="D77" s="3" t="n">
+        <v>8870.4</v>
+      </c>
       <c r="E77" s="3" t="n">
         <v>0</v>
       </c>
@@ -17530,7 +17682,9 @@
       <c r="C78" s="3" t="n">
         <v>36841.6</v>
       </c>
-      <c r="D78" s="3" t="n"/>
+      <c r="D78" s="3" t="n">
+        <v>8866.049999999999</v>
+      </c>
       <c r="E78" s="3" t="n">
         <v>0</v>
       </c>
@@ -17555,7 +17709,9 @@
       <c r="C79" s="3" t="n">
         <v>36272.1</v>
       </c>
-      <c r="D79" s="3" t="n"/>
+      <c r="D79" s="3" t="n">
+        <v>8867.440000000001</v>
+      </c>
       <c r="E79" s="3" t="n">
         <v>0</v>
       </c>
@@ -17580,7 +17736,9 @@
       <c r="C80" s="3" t="n">
         <v>36075.1</v>
       </c>
-      <c r="D80" s="3" t="n"/>
+      <c r="D80" s="3" t="n">
+        <v>8872.02</v>
+      </c>
       <c r="E80" s="3" t="n">
         <v>0</v>
       </c>
@@ -17605,7 +17763,9 @@
       <c r="C81" s="3" t="n">
         <v>35606.8</v>
       </c>
-      <c r="D81" s="3" t="n"/>
+      <c r="D81" s="3" t="n">
+        <v>8878.809999999999</v>
+      </c>
       <c r="E81" s="3" t="n">
         <v>0</v>
       </c>
@@ -17630,7 +17790,9 @@
       <c r="C82" s="3" t="n">
         <v>35014.9</v>
       </c>
-      <c r="D82" s="3" t="n"/>
+      <c r="D82" s="3" t="n">
+        <v>8875.879999999999</v>
+      </c>
       <c r="E82" s="3" t="n">
         <v>0</v>
       </c>
@@ -17655,7 +17817,9 @@
       <c r="C83" s="3" t="n">
         <v>34671.3</v>
       </c>
-      <c r="D83" s="3" t="n"/>
+      <c r="D83" s="3" t="n">
+        <v>8874.76</v>
+      </c>
       <c r="E83" s="3" t="n">
         <v>0</v>
       </c>
@@ -17680,7 +17844,9 @@
       <c r="C84" s="3" t="n">
         <v>34660.2</v>
       </c>
-      <c r="D84" s="3" t="n"/>
+      <c r="D84" s="3" t="n">
+        <v>8876.790000000001</v>
+      </c>
       <c r="E84" s="3" t="n">
         <v>0</v>
       </c>
@@ -17705,7 +17871,9 @@
       <c r="C85" s="3" t="n">
         <v>34285.2</v>
       </c>
-      <c r="D85" s="3" t="n"/>
+      <c r="D85" s="3" t="n">
+        <v>8875.77</v>
+      </c>
       <c r="E85" s="3" t="n">
         <v>0</v>
       </c>
@@ -17730,7 +17898,9 @@
       <c r="C86" s="3" t="n">
         <v>33958.5</v>
       </c>
-      <c r="D86" s="3" t="n"/>
+      <c r="D86" s="3" t="n">
+        <v>8859.9</v>
+      </c>
       <c r="E86" s="3" t="n">
         <v>0</v>
       </c>
@@ -17755,7 +17925,9 @@
       <c r="C87" s="3" t="n">
         <v>33657</v>
       </c>
-      <c r="D87" s="3" t="n"/>
+      <c r="D87" s="3" t="n">
+        <v>8859.27</v>
+      </c>
       <c r="E87" s="3" t="n">
         <v>0</v>
       </c>
@@ -17780,7 +17952,9 @@
       <c r="C88" s="3" t="n">
         <v>33385.9</v>
       </c>
-      <c r="D88" s="3" t="n"/>
+      <c r="D88" s="3" t="n">
+        <v>8856.459999999999</v>
+      </c>
       <c r="E88" s="3" t="n">
         <v>0</v>
       </c>
@@ -17805,7 +17979,9 @@
       <c r="C89" s="3" t="n">
         <v>33043.4</v>
       </c>
-      <c r="D89" s="3" t="n"/>
+      <c r="D89" s="3" t="n">
+        <v>8854.959999999999</v>
+      </c>
       <c r="E89" s="3" t="n">
         <v>0</v>
       </c>
@@ -17830,7 +18006,9 @@
       <c r="C90" s="3" t="n">
         <v>32765.2</v>
       </c>
-      <c r="D90" s="3" t="n"/>
+      <c r="D90" s="3" t="n">
+        <v>8803.33</v>
+      </c>
       <c r="E90" s="3" t="n">
         <v>0</v>
       </c>
@@ -17855,7 +18033,9 @@
       <c r="C91" s="3" t="n">
         <v>32586.9</v>
       </c>
-      <c r="D91" s="3" t="n"/>
+      <c r="D91" s="3" t="n">
+        <v>8803.299999999999</v>
+      </c>
       <c r="E91" s="3" t="n">
         <v>0</v>
       </c>
@@ -17880,7 +18060,9 @@
       <c r="C92" s="3" t="n">
         <v>31863.7</v>
       </c>
-      <c r="D92" s="3" t="n"/>
+      <c r="D92" s="3" t="n">
+        <v>8799.049999999999</v>
+      </c>
       <c r="E92" s="3" t="n">
         <v>0</v>
       </c>
@@ -17905,7 +18087,9 @@
       <c r="C93" s="3" t="n">
         <v>31330.7</v>
       </c>
-      <c r="D93" s="3" t="n"/>
+      <c r="D93" s="3" t="n">
+        <v>8796.74</v>
+      </c>
       <c r="E93" s="3" t="n">
         <v>0</v>
       </c>
@@ -17930,7 +18114,9 @@
       <c r="C94" s="3" t="n">
         <v>30595.8</v>
       </c>
-      <c r="D94" s="3" t="n"/>
+      <c r="D94" s="3" t="n">
+        <v>8797.290000000001</v>
+      </c>
       <c r="E94" s="3" t="n">
         <v>0</v>
       </c>
@@ -17955,7 +18141,9 @@
       <c r="C95" s="3" t="n">
         <v>30061.5</v>
       </c>
-      <c r="D95" s="3" t="n"/>
+      <c r="D95" s="3" t="n">
+        <v>8795.57</v>
+      </c>
       <c r="E95" s="3" t="n">
         <v>0</v>
       </c>
@@ -17980,7 +18168,9 @@
       <c r="C96" s="3" t="n">
         <v>29568.1</v>
       </c>
-      <c r="D96" s="3" t="n"/>
+      <c r="D96" s="3" t="n">
+        <v>8791.440000000001</v>
+      </c>
       <c r="E96" s="3" t="n">
         <v>0</v>
       </c>
@@ -18005,7 +18195,9 @@
       <c r="C97" s="3" t="n">
         <v>29535.8</v>
       </c>
-      <c r="D97" s="3" t="n"/>
+      <c r="D97" s="3" t="n">
+        <v>8791.870000000001</v>
+      </c>
       <c r="E97" s="3" t="n">
         <v>0</v>
       </c>
@@ -18107,7 +18299,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>发电总出力</t>
+          <t>日前非市场化机组总出力</t>
         </is>
       </c>
       <c r="B6" t="n">
